--- a/Newmont mining NV.xlsx
+++ b/Newmont mining NV.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srava\OneDrive\Desktop\newmont\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490AB3B9-6BE3-4B55-8B82-569DDC360829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACDC8697-82FC-45D3-B08B-D9098C757F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="819" xr2:uid="{416367EB-DAE2-4F67-8BDD-9C2E902ABEBE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="819" xr2:uid="{416367EB-DAE2-4F67-8BDD-9C2E902ABEBE}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="12" r:id="rId1"/>
@@ -4488,19 +4488,19 @@
                   <c:v>19304</c:v>
                 </c:pt>
                 <c:pt idx="6" formatCode="0">
-                  <c:v>22310</c:v>
+                  <c:v>23141.774999999998</c:v>
                 </c:pt>
                 <c:pt idx="7" formatCode="0">
-                  <c:v>25518.335266666661</c:v>
+                  <c:v>26579.621906666664</c:v>
                 </c:pt>
                 <c:pt idx="8" formatCode="0">
-                  <c:v>26119.764246833332</c:v>
+                  <c:v>27584.599759749999</c:v>
                 </c:pt>
                 <c:pt idx="9" formatCode="0">
-                  <c:v>27331.392161988333</c:v>
+                  <c:v>28482.751847494335</c:v>
                 </c:pt>
                 <c:pt idx="10" formatCode="0">
-                  <c:v>28684.157665016923</c:v>
+                  <c:v>29245.009135484819</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5780,9 +5780,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>95225</xdr:colOff>
+      <xdr:colOff>99035</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>22469</xdr:rowOff>
+      <xdr:rowOff>18659</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6295,7 +6295,7 @@
   <wetp:taskpane dockstate="right" visibility="0" width="0" row="0">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </wetp:taskpane>
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="7">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
     <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </wetp:taskpane>
 </wetp:taskpanes>
@@ -6341,6 +6341,7 @@
   </we:alternateReferences>
   <we:properties>
     <we:property name="Office.AutoShowTaskpaneWithDocument" value="true"/>
+    <we:property name="claude.fileId" value="&quot;3b0fa45c-60b8-44c6-a962-b1449b1793d6&quot;"/>
   </we:properties>
   <we:bindings/>
   <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
@@ -6439,7 +6440,7 @@
       </c>
       <c r="E11" s="24">
         <f ca="1">TODAY()</f>
-        <v>46110</v>
+        <v>46133</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
@@ -6504,7 +6505,7 @@
       </c>
       <c r="E15" s="27" t="str">
         <f ca="1">IF(E23&gt;=Ke!D32,"BUY","SELL")</f>
-        <v>SELL</v>
+        <v>BUY</v>
       </c>
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
@@ -6545,7 +6546,7 @@
       </c>
       <c r="E18" s="523">
         <f ca="1">DCF!B8</f>
-        <v>92.811830104634311</v>
+        <v>108.41662496285578</v>
       </c>
       <c r="F18" s="22"/>
       <c r="G18" s="22"/>
@@ -6559,7 +6560,7 @@
       </c>
       <c r="E19" s="523">
         <f ca="1">DCF!B9</f>
-        <v>98.258548128325188</v>
+        <v>114.20683162542262</v>
       </c>
       <c r="F19" s="22"/>
       <c r="G19" s="22"/>
@@ -6573,7 +6574,7 @@
       </c>
       <c r="E20" s="525">
         <f ca="1">E18/E17-1</f>
-        <v>-8.1070989063026677E-2</v>
+        <v>7.3431930325304817E-2</v>
       </c>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
@@ -6587,7 +6588,7 @@
       </c>
       <c r="E21" s="525">
         <f ca="1">E19/E17-1</f>
-        <v>-2.7143087838364499E-2</v>
+        <v>0.13076070916260019</v>
       </c>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
@@ -6621,7 +6622,7 @@
       </c>
       <c r="E23" s="527">
         <f ca="1">E21+E22</f>
-        <v>-1.7143087838364497E-2</v>
+        <v>0.14076070916260019</v>
       </c>
       <c r="F23" s="23"/>
       <c r="G23" s="23"/>
@@ -6753,23 +6754,23 @@
       </c>
       <c r="H3" s="36">
         <f>H4*'Income statement'!H4</f>
-        <v>1102.3246539926599</v>
+        <v>1026.0839737205506</v>
       </c>
       <c r="I3" s="36">
         <f>I4*'Income statement'!I4</f>
-        <v>1265.7368216443604</v>
+        <v>1175.8784607346097</v>
       </c>
       <c r="J3" s="36">
         <f>J4*'Income statement'!J4</f>
-        <v>1316.0462157420966</v>
+        <v>1221.9954053242013</v>
       </c>
       <c r="K3" s="36">
         <f>K4*'Income statement'!K4</f>
-        <v>1369.0827249214742</v>
+        <v>1270.6122054052976</v>
       </c>
       <c r="L3" s="159">
         <f>L4*'Income statement'!L4</f>
-        <v>1425.013997342937</v>
+        <v>1321.8825384583054</v>
       </c>
       <c r="M3" s="23"/>
     </row>
@@ -7074,23 +7075,23 @@
       </c>
       <c r="H10" s="575">
         <f t="shared" si="1"/>
-        <v>1517.011992493952</v>
+        <v>1440.7713122218427</v>
       </c>
       <c r="I10" s="575">
         <f t="shared" si="1"/>
-        <v>1710.2038708413002</v>
+        <v>1620.3455099315495</v>
       </c>
       <c r="J10" s="575">
         <f t="shared" si="1"/>
-        <v>1759.5709281857303</v>
+        <v>1665.520117767835</v>
       </c>
       <c r="K10" s="575">
         <f t="shared" si="1"/>
-        <v>1811.762653742217</v>
+        <v>1713.2921342260404</v>
       </c>
       <c r="L10" s="576">
         <f t="shared" si="1"/>
-        <v>1866.9469597049247</v>
+        <v>1763.815500820293</v>
       </c>
       <c r="M10" s="23"/>
     </row>
@@ -7275,23 +7276,23 @@
       </c>
       <c r="H18" s="298">
         <f>H19*'Income statement'!H4</f>
-        <v>1043.1801210350143</v>
+        <v>971.03008630070963</v>
       </c>
       <c r="I18" s="298">
         <f>I19*'Income statement'!I4</f>
-        <v>1197.8245120608817</v>
+        <v>1112.7874447410884</v>
       </c>
       <c r="J18" s="298">
         <f>J19*'Income statement'!J4</f>
-        <v>1245.43458739938</v>
+        <v>1156.4300138013787</v>
       </c>
       <c r="K18" s="298">
         <f>K19*'Income statement'!K4</f>
-        <v>1295.6254561825674</v>
+        <v>1202.4383101859671</v>
       </c>
       <c r="L18" s="299">
         <f>L19*'Income statement'!L4</f>
-        <v>1348.5557715147438</v>
+        <v>1250.9577659071292</v>
       </c>
       <c r="M18" s="23"/>
     </row>
@@ -7602,23 +7603,23 @@
       </c>
       <c r="H28" s="577">
         <f t="shared" si="2"/>
-        <v>2894.4242622924439</v>
+        <v>2822.2742275581395</v>
       </c>
       <c r="I28" s="577">
         <f t="shared" si="2"/>
-        <v>3219.3858341166547</v>
+        <v>3134.3487667968611</v>
       </c>
       <c r="J28" s="577">
         <f t="shared" si="2"/>
-        <v>3261.6064635728198</v>
+        <v>3172.6018899748183</v>
       </c>
       <c r="K28" s="577">
         <f t="shared" si="2"/>
-        <v>3306.9658158075126</v>
+        <v>3213.7786698109121</v>
       </c>
       <c r="L28" s="578">
         <f t="shared" si="2"/>
-        <v>3355.6240539960822</v>
+        <v>3258.0260483884676</v>
       </c>
       <c r="M28" s="23"/>
     </row>
@@ -7767,23 +7768,23 @@
       </c>
       <c r="H35" s="164">
         <f>H36*'Income statement'!H4</f>
-        <v>6726.2602471929467</v>
+        <v>6261.0482471929445</v>
       </c>
       <c r="I35" s="164">
         <f>I36*'Income statement'!I4</f>
-        <v>7723.3827947129457</v>
+        <v>7175.0772490862792</v>
       </c>
       <c r="J35" s="164">
         <f>J36*'Income statement'!J4</f>
-        <v>8030.3650220942263</v>
+        <v>7456.4776241857871</v>
       </c>
       <c r="K35" s="164">
         <f>K36*'Income statement'!K4</f>
-        <v>8353.9877969736754</v>
+        <v>7753.1318344919482</v>
       </c>
       <c r="L35" s="217">
         <f>L36*'Income statement'!L4</f>
-        <v>8695.274089447279</v>
+        <v>8065.977602592754</v>
       </c>
       <c r="M35" s="23"/>
     </row>
@@ -7952,23 +7953,23 @@
       </c>
       <c r="H42" s="270">
         <f>+G42+H46</f>
-        <v>56984.208376686387</v>
+        <v>56745.787226686385</v>
       </c>
       <c r="I42" s="270">
         <f>+H42+I46</f>
-        <v>60942.442058976769</v>
+        <v>60423.014316843102</v>
       </c>
       <c r="J42" s="270">
         <f>+I42+J46</f>
-        <v>65058.004132800059</v>
+        <v>64244.459099238316</v>
       </c>
       <c r="K42" s="270">
         <f>+J42+K46</f>
-        <v>69339.422878749072</v>
+        <v>68217.939164415438</v>
       </c>
       <c r="L42" s="271">
         <f>+K42+L46</f>
-        <v>73795.750849590797</v>
+        <v>72351.752685744228</v>
       </c>
       <c r="M42" s="23"/>
     </row>
@@ -7996,23 +7997,23 @@
       </c>
       <c r="H43" s="477">
         <f t="shared" ref="H43:L43" si="3">+H42*H45</f>
-        <v>19944.472931840235</v>
+        <v>19861.025529340233</v>
       </c>
       <c r="I43" s="477">
         <f t="shared" si="3"/>
-        <v>21329.854720641866</v>
+        <v>21148.055010895085</v>
       </c>
       <c r="J43" s="477">
         <f t="shared" si="3"/>
-        <v>22770.301446480018</v>
+        <v>22485.560684733409</v>
       </c>
       <c r="K43" s="477">
         <f t="shared" si="3"/>
-        <v>24268.798007562174</v>
+        <v>23876.278707545403</v>
       </c>
       <c r="L43" s="478">
         <f t="shared" si="3"/>
-        <v>25828.512797356776</v>
+        <v>25323.113440010478</v>
       </c>
       <c r="M43" s="23"/>
     </row>
@@ -8046,23 +8047,23 @@
       </c>
       <c r="H44" s="484">
         <f t="shared" ref="H44:L44" si="5">+H42-H43</f>
-        <v>37039.735444846156</v>
+        <v>36884.761697346155</v>
       </c>
       <c r="I44" s="484">
         <f t="shared" si="5"/>
-        <v>39612.587338334903</v>
+        <v>39274.959305948018</v>
       </c>
       <c r="J44" s="484">
         <f t="shared" si="5"/>
-        <v>42287.702686320044</v>
+        <v>41758.898414504903</v>
       </c>
       <c r="K44" s="484">
         <f t="shared" si="5"/>
-        <v>45070.624871186898</v>
+        <v>44341.660456870035</v>
       </c>
       <c r="L44" s="485">
         <f t="shared" si="5"/>
-        <v>47967.238052234025</v>
+        <v>47028.63924573375</v>
       </c>
       <c r="M44" s="23"/>
     </row>
@@ -8140,23 +8141,23 @@
       </c>
       <c r="H46" s="36">
         <f>H48*'Income statement'!H4</f>
-        <v>3447.2083766863848</v>
+        <v>3208.7872266863837</v>
       </c>
       <c r="I46" s="36">
         <f>I48*'Income statement'!I4</f>
-        <v>3958.233682290384</v>
+        <v>3677.2270901567176</v>
       </c>
       <c r="J46" s="36">
         <f>J48*'Income statement'!J4</f>
-        <v>4115.562073823291</v>
+        <v>3821.4447823952155</v>
       </c>
       <c r="K46" s="36">
         <f>K48*'Income statement'!K4</f>
-        <v>4281.4187459490076</v>
+        <v>3973.4800651771229</v>
       </c>
       <c r="L46" s="159">
         <f>L48*'Income statement'!L4</f>
-        <v>4456.3279708417303</v>
+        <v>4133.813521328786</v>
       </c>
       <c r="M46" s="23" t="s">
         <v>410</v>
@@ -12352,7 +12353,7 @@
       <c r="F3" s="30"/>
       <c r="G3" s="35">
         <f ca="1">TODAY()</f>
-        <v>46110</v>
+        <v>46133</v>
       </c>
       <c r="H3" s="30" t="s">
         <v>208</v>
@@ -12376,7 +12377,7 @@
       <c r="F4" s="30"/>
       <c r="G4" s="35">
         <f ca="1">G3+365</f>
-        <v>46475</v>
+        <v>46498</v>
       </c>
       <c r="H4" s="30" t="s">
         <v>210</v>
@@ -12398,7 +12399,7 @@
       <c r="F5" s="30"/>
       <c r="G5" s="35">
         <f ca="1">G4+366</f>
-        <v>46841</v>
+        <v>46864</v>
       </c>
       <c r="H5" s="30" t="s">
         <v>211</v>
@@ -12454,7 +12455,7 @@
       </c>
       <c r="B8" s="49">
         <f ca="1">B24</f>
-        <v>92.811830104634311</v>
+        <v>108.41662496285578</v>
       </c>
       <c r="C8" s="42"/>
       <c r="D8" s="30"/>
@@ -12466,7 +12467,7 @@
       <c r="H8" s="30"/>
       <c r="I8" s="50">
         <f ca="1">(B8-$B$6)/$B$6</f>
-        <v>-8.1070989063026622E-2</v>
+        <v>7.3431930325304734E-2</v>
       </c>
       <c r="J8" s="23"/>
       <c r="K8" s="23"/>
@@ -12478,7 +12479,7 @@
       </c>
       <c r="B9" s="49">
         <f ca="1">B46</f>
-        <v>98.258548128325188</v>
+        <v>114.20683162542262</v>
       </c>
       <c r="C9" s="52"/>
       <c r="D9" s="30"/>
@@ -12490,7 +12491,7 @@
       <c r="H9" s="30"/>
       <c r="I9" s="50">
         <f ca="1">(B9-$B$6)/$B$6</f>
-        <v>-2.7143087838364475E-2</v>
+        <v>0.13076070916260024</v>
       </c>
       <c r="J9" s="23"/>
       <c r="K9" s="23"/>
@@ -12586,23 +12587,23 @@
       <c r="C15" s="58"/>
       <c r="D15" s="58">
         <f ca="1">MAX((D14-$G$3)/365,0)</f>
-        <v>0.75890410958904109</v>
+        <v>0.69589041095890414</v>
       </c>
       <c r="E15" s="58">
         <f t="shared" ref="E15:G15" ca="1" si="0">MAX((E14-$G$3)/365,0)</f>
-        <v>1.7589041095890412</v>
+        <v>1.6958904109589041</v>
       </c>
       <c r="F15" s="58">
         <f t="shared" ca="1" si="0"/>
-        <v>2.7616438356164386</v>
+        <v>2.6986301369863015</v>
       </c>
       <c r="G15" s="58">
         <f t="shared" ca="1" si="0"/>
-        <v>3.7616438356164386</v>
+        <v>3.6986301369863015</v>
       </c>
       <c r="H15" s="58">
         <f ca="1">MAX((H14-$G$3)/365,0)</f>
-        <v>4.7616438356164386</v>
+        <v>4.6986301369863011</v>
       </c>
       <c r="I15" s="58"/>
       <c r="J15" s="55"/>
@@ -12617,23 +12618,23 @@
       <c r="C16" s="61"/>
       <c r="D16" s="61">
         <f ca="1">'Cash flow'!C61</f>
-        <v>4200.1447478653608</v>
+        <v>5326.1378346143938</v>
       </c>
       <c r="E16" s="61">
         <f ca="1">'Cash flow'!D61</f>
-        <v>7901.0438955053141</v>
+        <v>9408.7529746477703</v>
       </c>
       <c r="F16" s="61">
         <f ca="1">'Cash flow'!E61</f>
-        <v>7256.3157527199637</v>
+        <v>9139.8971339335094</v>
       </c>
       <c r="G16" s="61">
         <f ca="1">'Cash flow'!F61</f>
-        <v>7723.8663149187641</v>
+        <v>9344.6590272460817</v>
       </c>
       <c r="H16" s="61">
         <f ca="1">'Cash flow'!G61</f>
-        <v>8182.1351978390358</v>
+        <v>9399.7043724129999</v>
       </c>
       <c r="I16" s="61"/>
       <c r="J16" s="55"/>
@@ -12648,23 +12649,23 @@
       <c r="C17" s="62"/>
       <c r="D17" s="62">
         <f ca="1">D16*D15/((1+$B$3)^D15)</f>
-        <v>2979.2139041452588</v>
+        <v>3483.6999121837221</v>
       </c>
       <c r="E17" s="62">
         <f t="shared" ref="E17:F17" ca="1" si="1">E16/((1+$B$3)^E15)</f>
-        <v>6755.5622678896025</v>
+        <v>8089.9540188065548</v>
       </c>
       <c r="F17" s="62">
         <f t="shared" ca="1" si="1"/>
-        <v>5674.3189967751705</v>
+        <v>7187.4666531886387</v>
       </c>
       <c r="G17" s="62">
         <f ca="1">G16/((1+$B$3)^G15)</f>
-        <v>5525.3376908258315</v>
+        <v>6722.4022641561896</v>
       </c>
       <c r="H17" s="62">
         <f ca="1">H16/((1+$B$3)^H15)</f>
-        <v>5354.4791466498646</v>
+        <v>6185.8834809585196</v>
       </c>
       <c r="I17" s="62"/>
       <c r="J17" s="55"/>
@@ -12723,7 +12724,7 @@
       </c>
       <c r="B21" s="40">
         <f ca="1">H16*(1+B19)/(B3-B19)</f>
-        <v>114115.87878321706</v>
+        <v>131097.26236785401</v>
       </c>
       <c r="C21" s="67"/>
       <c r="D21" s="68" t="s">
@@ -12744,7 +12745,7 @@
       </c>
       <c r="B22" s="69">
         <f ca="1">B21/(1+B3)^(H15)</f>
-        <v>74678.684533071195</v>
+        <v>86274.244119872616</v>
       </c>
       <c r="C22" s="40"/>
       <c r="D22" s="68"/>
@@ -12763,7 +12764,7 @@
       </c>
       <c r="B23" s="40">
         <f ca="1">SUM(D17:H17)+B22</f>
-        <v>100967.59653935692</v>
+        <v>117943.65044916625</v>
       </c>
       <c r="C23" s="40"/>
       <c r="D23" s="68"/>
@@ -12782,7 +12783,7 @@
       </c>
       <c r="B24" s="71">
         <f ca="1">B23/I3</f>
-        <v>92.811830104634311</v>
+        <v>108.41662496285578</v>
       </c>
       <c r="C24" s="53"/>
       <c r="D24" s="53"/>
@@ -12815,7 +12816,7 @@
       <c r="A26" s="30"/>
       <c r="B26" s="73">
         <f ca="1">B24</f>
-        <v>92.811830104634311</v>
+        <v>108.41662496285578</v>
       </c>
       <c r="C26" s="74">
         <f>D26-L27</f>
@@ -12858,25 +12859,25 @@
       </c>
       <c r="C27" s="78">
         <f t="dataTable" ref="C27:I33" dt2D="1" dtr="1" r1="B19" r2="B3" ca="1"/>
-        <v>68.18317633961874</v>
+        <v>79.988826668525277</v>
       </c>
       <c r="D27" s="79">
-        <v>70.70836553565924</v>
+        <v>82.908615187776945</v>
       </c>
       <c r="E27" s="79">
-        <v>73.504689089507465</v>
+        <v>86.141906943278443</v>
       </c>
       <c r="F27" s="80">
-        <v>76.618292692484047</v>
+        <v>89.742058594381092</v>
       </c>
       <c r="G27" s="79">
-        <v>80.106423524808235</v>
+        <v>93.775263066282633</v>
       </c>
       <c r="H27" s="79">
-        <v>84.040982312002484</v>
+        <v>98.324656669416967</v>
       </c>
       <c r="I27" s="81">
-        <v>88.513532451121222</v>
+        <v>103.49611097804971</v>
       </c>
       <c r="J27" s="55"/>
       <c r="K27" s="55"/>
@@ -12891,25 +12892,25 @@
         <v>0.10313423855456674</v>
       </c>
       <c r="C28" s="82">
-        <v>71.805655906059826</v>
+        <v>84.167687858858756</v>
       </c>
       <c r="D28" s="83">
-        <v>74.649955405966054</v>
+        <v>87.455515478502377</v>
       </c>
       <c r="E28" s="83">
-        <v>77.81697846331754</v>
+        <v>91.116390811902349</v>
       </c>
       <c r="F28" s="84">
-        <v>81.364954436388942</v>
+        <v>95.217623258935689</v>
       </c>
       <c r="G28" s="83">
-        <v>85.367017636610242</v>
+        <v>99.843751388438534</v>
       </c>
       <c r="H28" s="83">
-        <v>89.916302395340779</v>
+        <v>105.10243250829642</v>
       </c>
       <c r="I28" s="85">
-        <v>95.133281525541648</v>
+        <v>111.13292545601325</v>
       </c>
       <c r="J28" s="55"/>
       <c r="K28" s="55"/>
@@ -12922,25 +12923,25 @@
         <v>9.8134238554566738E-2</v>
       </c>
       <c r="C29" s="82">
-        <v>75.819340698423844</v>
+        <v>88.796384197414838</v>
       </c>
       <c r="D29" s="83">
-        <v>79.040948671973638</v>
+        <v>92.519290312966675</v>
       </c>
       <c r="E29" s="86">
-        <v>82.650075437968397</v>
+        <v>96.690015062607259</v>
       </c>
       <c r="F29" s="87">
-        <v>86.721115807110962</v>
+        <v>101.39452945770887</v>
       </c>
       <c r="G29" s="88">
-        <v>91.34880931842099</v>
+        <v>106.7423149783574</v>
       </c>
       <c r="H29" s="83">
-        <v>96.655705182246308</v>
+        <v>112.87499009843485</v>
       </c>
       <c r="I29" s="85">
-        <v>102.80317439982144</v>
+        <v>119.97903594547161</v>
       </c>
       <c r="J29" s="55"/>
       <c r="K29" s="55"/>
@@ -12955,25 +12956,25 @@
         <v>9.3134238554566734E-2</v>
       </c>
       <c r="C30" s="91">
-        <v>80.290862119455937</v>
+        <v>93.951492705578147</v>
       </c>
       <c r="D30" s="92">
-        <v>83.962479956997427</v>
+        <v>98.193212489630483</v>
       </c>
       <c r="E30" s="93">
-        <v>88.104009309063642</v>
+        <v>102.97780820906296</v>
       </c>
       <c r="F30" s="94">
-        <v>92.811830104634311</v>
+        <v>108.41662496285578</v>
       </c>
       <c r="G30" s="95">
-        <v>98.210613461091313</v>
+        <v>114.65369188707308</v>
       </c>
       <c r="H30" s="92">
-        <v>104.46452447570343</v>
+        <v>121.87866443381989</v>
       </c>
       <c r="I30" s="96">
-        <v>111.79420618416265</v>
+        <v>130.34644547456031</v>
       </c>
       <c r="J30" s="55"/>
       <c r="K30" s="55"/>
@@ -12986,25 +12987,25 @@
         <v>8.813423855456673E-2</v>
       </c>
       <c r="C31" s="82">
-        <v>85.302882879771857</v>
+        <v>99.728013268579716</v>
       </c>
       <c r="D31" s="83">
-        <v>89.516453308106932</v>
+        <v>104.59443003223633</v>
       </c>
       <c r="E31" s="97">
-        <v>94.306165706552392</v>
+        <v>110.12625561942583</v>
       </c>
       <c r="F31" s="98">
-        <v>99.798859821687898</v>
+        <v>116.46998219861945</v>
       </c>
       <c r="G31" s="99">
-        <v>106.16155636987527</v>
+        <v>123.81850850683972</v>
       </c>
       <c r="H31" s="83">
-        <v>113.61873642836365</v>
+        <v>132.43109649212536</v>
       </c>
       <c r="I31" s="85">
-        <v>122.47937690359063</v>
+        <v>142.66459562991409</v>
       </c>
       <c r="J31" s="55"/>
       <c r="K31" s="55"/>
@@ -13017,25 +13018,25 @@
         <v>8.3134238554566725E-2</v>
       </c>
       <c r="C32" s="82">
-        <v>90.959226462380741</v>
+        <v>106.24526326479764</v>
       </c>
       <c r="D32" s="83">
-        <v>95.832642007524257</v>
+        <v>111.87212763318379</v>
       </c>
       <c r="E32" s="83">
-        <v>101.42132430379472</v>
+        <v>118.32484174873926</v>
       </c>
       <c r="F32" s="84">
-        <v>107.89521285648348</v>
+        <v>125.79961841914417</v>
       </c>
       <c r="G32" s="83">
-        <v>115.48271168663582</v>
+        <v>134.56017380726436</v>
       </c>
       <c r="H32" s="83">
-        <v>124.49819726065776</v>
+        <v>144.96948819267851</v>
       </c>
       <c r="I32" s="85">
-        <v>135.38667092896549</v>
+        <v>157.54136184941336</v>
       </c>
       <c r="J32" s="55"/>
       <c r="K32" s="55"/>
@@ -13048,25 +13049,25 @@
         <v>7.8134238554566721E-2</v>
       </c>
       <c r="C33" s="100">
-        <v>97.392110719267535</v>
+        <v>113.65519019936016</v>
       </c>
       <c r="D33" s="101">
-        <v>103.07891448466022</v>
+        <v>120.21928163978578</v>
       </c>
       <c r="E33" s="101">
-        <v>109.66646622699687</v>
+        <v>127.82307698584295</v>
       </c>
       <c r="F33" s="102">
-        <v>117.38718009652881</v>
+        <v>136.73484428356161</v>
       </c>
       <c r="G33" s="101">
-        <v>126.56095212207494</v>
+        <v>147.32382904786098</v>
       </c>
       <c r="H33" s="101">
-        <v>137.6405966203198</v>
+        <v>160.11270002253335</v>
       </c>
       <c r="I33" s="103">
-        <v>151.28888377217922</v>
+        <v>175.86647113297457</v>
       </c>
       <c r="J33" s="55"/>
       <c r="K33" s="55"/>
@@ -13171,19 +13172,19 @@
       </c>
       <c r="E39" s="58">
         <f t="shared" ref="E39:G39" ca="1" si="3">MAX((E38-$G$4)/365,0)</f>
-        <v>0.75890410958904109</v>
+        <v>0.69589041095890414</v>
       </c>
       <c r="F39" s="58">
         <f t="shared" ca="1" si="3"/>
-        <v>1.7616438356164383</v>
+        <v>1.6986301369863013</v>
       </c>
       <c r="G39" s="58">
         <f t="shared" ca="1" si="3"/>
-        <v>2.7616438356164386</v>
+        <v>2.6986301369863015</v>
       </c>
       <c r="H39" s="58">
         <f ca="1">MAX((H38-$G$4)/365,0)</f>
-        <v>3.7616438356164386</v>
+        <v>3.6986301369863015</v>
       </c>
       <c r="I39" s="58"/>
       <c r="J39" s="55"/>
@@ -13202,19 +13203,19 @@
       </c>
       <c r="E40" s="69">
         <f t="shared" ref="E40:G40" ca="1" si="4">E16</f>
-        <v>7901.0438955053141</v>
+        <v>9408.7529746477703</v>
       </c>
       <c r="F40" s="69">
         <f t="shared" ca="1" si="4"/>
-        <v>7256.3157527199637</v>
+        <v>9139.8971339335094</v>
       </c>
       <c r="G40" s="69">
         <f t="shared" ca="1" si="4"/>
-        <v>7723.8663149187641</v>
+        <v>9344.6590272460817</v>
       </c>
       <c r="H40" s="69">
         <f ca="1">H16</f>
-        <v>8182.1351978390358</v>
+        <v>9399.7043724129999</v>
       </c>
       <c r="I40" s="69"/>
       <c r="J40" s="55"/>
@@ -13233,19 +13234,19 @@
       </c>
       <c r="E41" s="62">
         <f ca="1">E40*E39/((1+$B$3)^E39)</f>
-        <v>5604.3068141198282</v>
+        <v>6154.0412451439688</v>
       </c>
       <c r="F41" s="62">
         <f ca="1">F40/((1+$B$3)^F39)</f>
-        <v>6202.7923758555398</v>
+        <v>7856.8658870697036</v>
       </c>
       <c r="G41" s="62">
         <f ca="1">G40/((1+$B$3)^G39)</f>
-        <v>6039.9358094177433</v>
+        <v>7348.4880802858715</v>
       </c>
       <c r="H41" s="62">
         <f ca="1">H40/((1+$B$3)^H39)</f>
-        <v>5853.1644848294063</v>
+        <v>6762.001028744864</v>
       </c>
       <c r="I41" s="62"/>
       <c r="J41" s="55"/>
@@ -13272,7 +13273,7 @@
       </c>
       <c r="B43" s="40">
         <f ca="1">H40*(1+B19)/(B3-B19)</f>
-        <v>114115.87878321706</v>
+        <v>131097.26236785401</v>
       </c>
       <c r="C43" s="68"/>
       <c r="D43" s="40"/>
@@ -13291,7 +13292,7 @@
       </c>
       <c r="B44" s="69">
         <f ca="1">B43/(1+B3)^H39</f>
-        <v>81633.826953315496</v>
+        <v>94309.33015284776</v>
       </c>
       <c r="C44" s="68"/>
       <c r="D44" s="40"/>
@@ -13310,7 +13311,7 @@
       </c>
       <c r="B45" s="40">
         <f ca="1">SUM(D41:H41)+B44</f>
-        <v>105334.02643753801</v>
+        <v>122430.72639409217</v>
       </c>
       <c r="C45" s="68"/>
       <c r="D45" s="40"/>
@@ -13329,7 +13330,7 @@
       </c>
       <c r="B46" s="105">
         <f ca="1">B45/I4</f>
-        <v>98.258548128325188</v>
+        <v>114.20683162542262</v>
       </c>
       <c r="C46" s="106"/>
       <c r="D46" s="106"/>
@@ -13362,7 +13363,7 @@
       <c r="A48" s="30"/>
       <c r="B48" s="73">
         <f ca="1">B46</f>
-        <v>98.258548128325188</v>
+        <v>114.20683162542262</v>
       </c>
       <c r="C48" s="74">
         <f>D48-$L$26</f>
@@ -13403,25 +13404,25 @@
       </c>
       <c r="C49" s="78">
         <f t="dataTable" ref="C49:I55" dt2D="1" dtr="1" r1="B19" r2="B3" ca="1"/>
-        <v>71.982653896778132</v>
+        <v>83.89804103441972</v>
       </c>
       <c r="D49" s="79">
-        <v>74.82231580179257</v>
+        <v>87.181443419404658</v>
       </c>
       <c r="E49" s="79">
-        <v>77.966877596373465</v>
+        <v>90.81739095168912</v>
       </c>
       <c r="F49" s="80">
-        <v>81.468231693940481</v>
+        <v>94.86588502569397</v>
       </c>
       <c r="G49" s="79">
-        <v>85.390754513136997</v>
+        <v>99.401361857271965</v>
       </c>
       <c r="H49" s="79">
-        <v>89.815300887149021</v>
+        <v>104.5173110804009</v>
       </c>
       <c r="I49" s="81">
-        <v>94.844836998042027</v>
+        <v>110.33278891341779</v>
       </c>
       <c r="J49" s="55"/>
       <c r="K49" s="55"/>
@@ -13434,25 +13435,25 @@
         <v>0.10313423855456674</v>
       </c>
       <c r="C50" s="82">
-        <v>75.689585029764743</v>
+        <v>88.167316706920829</v>
       </c>
       <c r="D50" s="83">
-        <v>78.873665450332652</v>
+        <v>91.847909257126901</v>
       </c>
       <c r="E50" s="83">
-        <v>82.419022086907844</v>
+        <v>95.946113919330429</v>
       </c>
       <c r="F50" s="84">
-        <v>86.390840395378717</v>
+        <v>100.53728089567288</v>
       </c>
       <c r="G50" s="83">
-        <v>90.870991335221774</v>
+        <v>105.71604775924477</v>
       </c>
       <c r="H50" s="83">
-        <v>95.963735094569017</v>
+        <v>111.60293259408783</v>
       </c>
       <c r="I50" s="85">
-        <v>101.80393620683999</v>
+        <v>118.35383014261643</v>
       </c>
       <c r="J50" s="55"/>
       <c r="K50" s="55"/>
@@ -13465,25 +13466,25 @@
         <v>9.8134238554566738E-2</v>
       </c>
       <c r="C51" s="82">
-        <v>79.795675214273999</v>
+        <v>92.8954304893212</v>
       </c>
       <c r="D51" s="83">
-        <v>83.385791064094462</v>
+        <v>97.044186130160043</v>
       </c>
       <c r="E51" s="86">
-        <v>87.407752554440506</v>
+        <v>101.69198473006989</v>
       </c>
       <c r="F51" s="87">
-        <v>91.944464244538921</v>
+        <v>106.93463120792561</v>
       </c>
       <c r="G51" s="88">
-        <v>97.101502580509688</v>
+        <v>112.89413022728196</v>
       </c>
       <c r="H51" s="83">
-        <v>103.01543472572742</v>
+        <v>119.72829947790301</v>
       </c>
       <c r="I51" s="85">
-        <v>109.86609031619686</v>
+        <v>127.64495097699755</v>
       </c>
       <c r="J51" s="55"/>
       <c r="K51" s="55"/>
@@ -13498,25 +13499,25 @@
         <v>9.3134238554566734E-2</v>
       </c>
       <c r="C52" s="91">
-        <v>84.368884083297587</v>
+        <v>98.160482201136006</v>
       </c>
       <c r="D52" s="92">
-        <v>88.441854985032194</v>
+        <v>102.86587421582495</v>
       </c>
       <c r="E52" s="93">
-        <v>93.036104519166827</v>
+        <v>108.17348519389481</v>
       </c>
       <c r="F52" s="94">
-        <v>98.258548128325188</v>
+        <v>114.20683162542262</v>
       </c>
       <c r="G52" s="95">
-        <v>104.24748501897457</v>
+        <v>121.12568680549182</v>
       </c>
       <c r="H52" s="92">
-        <v>111.18502555603891</v>
+        <v>129.14043786368896</v>
       </c>
       <c r="I52" s="96">
-        <v>119.31593177734671</v>
+        <v>138.53385169574767</v>
       </c>
       <c r="J52" s="55"/>
       <c r="K52" s="55"/>
@@ -13529,25 +13530,25 @@
         <v>8.813423855456673E-2</v>
       </c>
       <c r="C53" s="82">
-        <v>89.493521295055515</v>
+        <v>104.05936067617209</v>
       </c>
       <c r="D53" s="83">
-        <v>94.146307232174777</v>
+        <v>109.43304455477521</v>
       </c>
       <c r="E53" s="97">
-        <v>99.435291211288771</v>
+        <v>115.54149835575789</v>
       </c>
       <c r="F53" s="98">
-        <v>105.50053454125448</v>
+        <v>122.54648434533925</v>
       </c>
       <c r="G53" s="99">
-        <v>112.52646789755558</v>
+        <v>130.66100870109997</v>
       </c>
       <c r="H53" s="83">
-        <v>120.76097188813218</v>
+        <v>140.17135840135956</v>
       </c>
       <c r="I53" s="85">
-        <v>130.54523065351745</v>
+        <v>151.47158031188764</v>
       </c>
       <c r="J53" s="55"/>
       <c r="K53" s="55"/>
@@ -13560,25 +13561,25 @@
         <v>8.3134238554566725E-2</v>
       </c>
       <c r="C54" s="82">
-        <v>95.275477943030126</v>
+        <v>110.71375554057583</v>
       </c>
       <c r="D54" s="83">
-        <v>100.63216244068227</v>
+        <v>116.89860410383081</v>
       </c>
       <c r="E54" s="83">
-        <v>106.77504263249511</v>
+        <v>123.99119724521029</v>
       </c>
       <c r="F54" s="84">
-        <v>113.89090995972798</v>
+        <v>132.20720508260283</v>
       </c>
       <c r="G54" s="83">
-        <v>122.23081797350969</v>
+        <v>141.83649501358994</v>
       </c>
       <c r="H54" s="83">
-        <v>132.14031806965787</v>
+        <v>153.27804201138306</v>
       </c>
       <c r="I54" s="85">
-        <v>144.10853985617084</v>
+        <v>167.09659700626392</v>
       </c>
       <c r="J54" s="55"/>
       <c r="K54" s="55"/>
@@ -13591,25 +13592,25 @@
         <v>7.8134238554566721E-2</v>
       </c>
       <c r="C55" s="100">
-        <v>101.84960391514686</v>
+        <v>118.27863504994046</v>
       </c>
       <c r="D55" s="101">
-        <v>108.07148089075839</v>
+        <v>125.46034398238729</v>
       </c>
       <c r="E55" s="101">
-        <v>115.27885751253004</v>
+        <v>133.77958289806816</v>
       </c>
       <c r="F55" s="102">
-        <v>123.72601585346999</v>
+        <v>143.52986127044926</v>
       </c>
       <c r="G55" s="101">
-        <v>133.76295106347425</v>
+        <v>155.11516704467553</v>
       </c>
       <c r="H55" s="101">
-        <v>145.88508290510828</v>
+        <v>169.10734703611689</v>
       </c>
       <c r="I55" s="103">
-        <v>160.81754182051193</v>
+        <v>186.34339557846371</v>
       </c>
       <c r="J55" s="55"/>
       <c r="K55" s="55"/>
@@ -14714,23 +14715,23 @@
       </c>
       <c r="H4" s="147">
         <f>H24*(H15/1000)</f>
-        <v>22310</v>
+        <v>23141.774999999998</v>
       </c>
       <c r="I4" s="147">
         <f t="shared" ref="I4:L4" si="0">I24*(I15/1000)</f>
-        <v>25518.335266666661</v>
+        <v>26579.621906666664</v>
       </c>
       <c r="J4" s="147">
         <f t="shared" si="0"/>
-        <v>26119.764246833332</v>
+        <v>27584.599759749999</v>
       </c>
       <c r="K4" s="147">
         <f t="shared" si="0"/>
-        <v>27331.392161988333</v>
+        <v>28482.751847494335</v>
       </c>
       <c r="L4" s="148">
         <f t="shared" si="0"/>
-        <v>28684.157665016923</v>
+        <v>29245.009135484819</v>
       </c>
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
@@ -14945,23 +14946,23 @@
       </c>
       <c r="H9" s="151">
         <f t="shared" si="2"/>
-        <v>26778.995999999999</v>
+        <v>27610.771000000001</v>
       </c>
       <c r="I9" s="151">
         <f t="shared" si="2"/>
-        <v>30539.529933333328</v>
+        <v>31600.81657333333</v>
       </c>
       <c r="J9" s="151">
         <f t="shared" si="2"/>
-        <v>31255.5709135</v>
+        <v>32720.406426416666</v>
       </c>
       <c r="K9" s="151">
         <f t="shared" si="2"/>
-        <v>32737.834161988332</v>
+        <v>33889.193847494331</v>
       </c>
       <c r="L9" s="152">
         <f t="shared" si="2"/>
-        <v>34181.18166501692</v>
+        <v>34742.033135484817</v>
       </c>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
@@ -15449,23 +15450,23 @@
       </c>
       <c r="H24" s="23">
         <f>CHOOSE(Cover!$I$14,Revenue!H30,Revenue!H31,Revenue!H32)</f>
-        <v>4600</v>
+        <v>4771.5</v>
       </c>
       <c r="I24" s="23">
         <f>CHOOSE(Cover!$I$14,Revenue!I30,Revenue!I31,Revenue!I32)</f>
-        <v>4732</v>
+        <v>4928.8</v>
       </c>
       <c r="J24" s="23">
         <f>CHOOSE(Cover!$I$14,Revenue!J30,Revenue!J31,Revenue!J32)</f>
-        <v>4859</v>
+        <v>5131.5</v>
       </c>
       <c r="K24" s="23">
         <f>CHOOSE(Cover!$I$14,Revenue!K30,Revenue!K31,Revenue!K32)</f>
-        <v>5099</v>
+        <v>5313.8</v>
       </c>
       <c r="L24" s="158">
         <f>CHOOSE(Cover!$I$14,Revenue!L30,Revenue!L31,Revenue!L32)</f>
-        <v>5365</v>
+        <v>5469.9</v>
       </c>
       <c r="M24" s="23" t="s">
         <v>358</v>
@@ -15694,23 +15695,23 @@
       <c r="G30" s="23"/>
       <c r="H30" s="23">
         <f>H31+200</f>
-        <v>4800</v>
+        <v>4971.5</v>
       </c>
       <c r="I30" s="23">
         <f t="shared" ref="I30:L30" si="7">I31+200</f>
-        <v>4932</v>
+        <v>5128.8</v>
       </c>
       <c r="J30" s="23">
         <f t="shared" si="7"/>
-        <v>5059</v>
+        <v>5331.5</v>
       </c>
       <c r="K30" s="23">
         <f t="shared" si="7"/>
-        <v>5299</v>
+        <v>5513.8</v>
       </c>
       <c r="L30" s="23">
         <f t="shared" si="7"/>
-        <v>5565</v>
+        <v>5669.9</v>
       </c>
       <c r="M30" s="23" t="s">
         <v>351</v>
@@ -15726,19 +15727,19 @@
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
       <c r="H31" s="23">
-        <v>4600</v>
+        <v>4771.5</v>
       </c>
       <c r="I31" s="23">
-        <v>4732</v>
+        <v>4928.8</v>
       </c>
       <c r="J31" s="23">
-        <v>4859</v>
+        <v>5131.5</v>
       </c>
       <c r="K31" s="23">
-        <v>5099</v>
+        <v>5313.8</v>
       </c>
       <c r="L31" s="23">
-        <v>5365</v>
+        <v>5469.9</v>
       </c>
       <c r="M31" s="23" t="s">
         <v>352</v>
@@ -15757,23 +15758,23 @@
       <c r="G32" s="23"/>
       <c r="H32" s="23">
         <f>H31-200</f>
-        <v>4400</v>
+        <v>4571.5</v>
       </c>
       <c r="I32" s="23">
         <f t="shared" ref="I32:L32" si="8">I31-200</f>
-        <v>4532</v>
+        <v>4728.8</v>
       </c>
       <c r="J32" s="23">
         <f t="shared" si="8"/>
-        <v>4659</v>
+        <v>4931.5</v>
       </c>
       <c r="K32" s="23">
         <f t="shared" si="8"/>
-        <v>4899</v>
+        <v>5113.8</v>
       </c>
       <c r="L32" s="23">
         <f t="shared" si="8"/>
-        <v>5165</v>
+        <v>5269.9</v>
       </c>
       <c r="M32" s="23" t="s">
         <v>353</v>
@@ -16810,23 +16811,23 @@
       </c>
       <c r="H3" s="190">
         <f>H12*H44/1000</f>
-        <v>6978.18</v>
+        <v>6396.665</v>
       </c>
       <c r="I3" s="190">
         <f>I12*I44/1000</f>
-        <v>8224.5831843999986</v>
+        <v>7539.2012523666663</v>
       </c>
       <c r="J3" s="190">
         <f>J12*J44/1000</f>
-        <v>8608.3109686265998</v>
+        <v>7890.9517212410501</v>
       </c>
       <c r="K3" s="190">
         <f>K12*K44/1000</f>
-        <v>9012.8394372259099</v>
+        <v>8261.7694841237517</v>
       </c>
       <c r="L3" s="191">
         <f>L12*L44/1000</f>
-        <v>9439.4473028179164</v>
+        <v>8652.8266942497594</v>
       </c>
       <c r="M3" s="23"/>
       <c r="N3" s="23"/>
@@ -17046,23 +17047,23 @@
       </c>
       <c r="H8" s="550">
         <f t="shared" si="4"/>
-        <v>8407.8253089911832</v>
+        <v>7826.3103089911801</v>
       </c>
       <c r="I8" s="550">
         <f t="shared" si="4"/>
-        <v>9654.2284933911815</v>
+        <v>8968.8465613578483</v>
       </c>
       <c r="J8" s="550">
         <f t="shared" si="4"/>
-        <v>10037.956277617783</v>
+        <v>9320.597030232233</v>
       </c>
       <c r="K8" s="550">
         <f t="shared" si="4"/>
-        <v>10442.484746217093</v>
+        <v>9691.4147931149346</v>
       </c>
       <c r="L8" s="551">
         <f t="shared" si="4"/>
-        <v>10869.092611809099</v>
+        <v>10082.472003240942</v>
       </c>
       <c r="M8" s="23"/>
       <c r="N8" s="23"/>
@@ -17176,23 +17177,23 @@
       </c>
       <c r="H12" s="199">
         <f>G12*(1+H13)</f>
-        <v>1438.8</v>
+        <v>1318.9</v>
       </c>
       <c r="I12" s="199">
         <f>H12*(1+I13)</f>
-        <v>1525.1279999999999</v>
+        <v>1398.0340000000001</v>
       </c>
       <c r="J12" s="199">
         <f t="shared" ref="J12:L12" si="5">I12*(1+J13)</f>
-        <v>1601.3843999999999</v>
+        <v>1467.9357000000002</v>
       </c>
       <c r="K12" s="199">
         <f t="shared" si="5"/>
-        <v>1681.45362</v>
+        <v>1541.3324850000004</v>
       </c>
       <c r="L12" s="200">
         <f t="shared" si="5"/>
-        <v>1765.5263010000001</v>
+        <v>1618.3991092500005</v>
       </c>
       <c r="M12" s="23"/>
       <c r="N12" s="23"/>
@@ -17223,7 +17224,7 @@
       </c>
       <c r="H13" s="502">
         <f>CHOOSE(Cover!$I$15,'Cost of sales'!H14,'Cost of sales'!H15,'Cost of sales'!H16)</f>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I13" s="502">
         <f>CHOOSE(Cover!$I$15,'Cost of sales'!I14,'Cost of sales'!I15,'Cost of sales'!I16)</f>
@@ -17255,7 +17256,7 @@
       <c r="G14" s="201"/>
       <c r="H14" s="201">
         <f>H15-0.01</f>
-        <v>0.19</v>
+        <v>9.0000000000000011E-2</v>
       </c>
       <c r="I14" s="201">
         <f t="shared" ref="I14:L14" si="7">I15-0.01</f>
@@ -17288,7 +17289,7 @@
       <c r="F15" s="502"/>
       <c r="G15" s="502"/>
       <c r="H15" s="502">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="I15" s="502">
         <v>0.06</v>
@@ -17318,7 +17319,7 @@
       <c r="G16" s="201"/>
       <c r="H16" s="201">
         <f>H15+0.01</f>
-        <v>0.21000000000000002</v>
+        <v>0.11</v>
       </c>
       <c r="I16" s="201">
         <f t="shared" ref="I16:L16" si="8">I15+0.01</f>
@@ -19175,23 +19176,23 @@
       </c>
       <c r="H3" s="164">
         <f>Revenue!H9</f>
-        <v>26778.995999999999</v>
+        <v>27610.771000000001</v>
       </c>
       <c r="I3" s="164">
         <f>Revenue!I9</f>
-        <v>30539.529933333328</v>
+        <v>31600.81657333333</v>
       </c>
       <c r="J3" s="164">
         <f>Revenue!J9</f>
-        <v>31255.5709135</v>
+        <v>32720.406426416666</v>
       </c>
       <c r="K3" s="164">
         <f>Revenue!K9</f>
-        <v>32737.834161988332</v>
+        <v>33889.193847494331</v>
       </c>
       <c r="L3" s="217">
         <f>Revenue!L9</f>
-        <v>34181.18166501692</v>
+        <v>34742.033135484817</v>
       </c>
       <c r="M3" s="23"/>
       <c r="N3" s="23"/>
@@ -19220,23 +19221,23 @@
       </c>
       <c r="H4" s="456">
         <f>'Cost of sales'!H8</f>
-        <v>8407.8253089911832</v>
+        <v>7826.3103089911801</v>
       </c>
       <c r="I4" s="456">
         <f>'Cost of sales'!I8</f>
-        <v>9654.2284933911815</v>
+        <v>8968.8465613578483</v>
       </c>
       <c r="J4" s="456">
         <f>'Cost of sales'!J8</f>
-        <v>10037.956277617783</v>
+        <v>9320.597030232233</v>
       </c>
       <c r="K4" s="456">
         <f>'Cost of sales'!K8</f>
-        <v>10442.484746217093</v>
+        <v>9691.4147931149346</v>
       </c>
       <c r="L4" s="457">
         <f>'Cost of sales'!L8</f>
-        <v>10869.092611809099</v>
+        <v>10082.472003240942</v>
       </c>
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
@@ -19265,23 +19266,23 @@
       </c>
       <c r="H5" s="209">
         <f>H31*'Balance sheet'!H13</f>
-        <v>2807.6119467193389</v>
+        <v>2795.8649366588388</v>
       </c>
       <c r="I5" s="209">
         <f>I31*'Balance sheet'!I13</f>
-        <v>3002.6341202457857</v>
+        <v>2977.0419153908601</v>
       </c>
       <c r="J5" s="209">
         <f>J31*'Balance sheet'!J13</f>
-        <v>3205.4078636230597</v>
+        <v>3165.3244998194718</v>
       </c>
       <c r="K5" s="209">
         <f>K31*'Balance sheet'!K13</f>
-        <v>3416.353365235967</v>
+        <v>3361.0978626307488</v>
       </c>
       <c r="L5" s="210">
         <f>L31*'Balance sheet'!L13</f>
-        <v>3635.9166443593394</v>
+        <v>3564.7708548266187</v>
       </c>
       <c r="M5" s="23"/>
       <c r="N5" s="23"/>
@@ -19310,23 +19311,23 @@
       </c>
       <c r="H6" s="459">
         <f>H32*'Balance sheet'!H32</f>
-        <v>370.61693962033138</v>
+        <v>344.98375842033124</v>
       </c>
       <c r="I6" s="459">
         <f>I32*'Balance sheet'!I32</f>
-        <v>365.48066620900926</v>
+        <v>339.53412420426633</v>
       </c>
       <c r="J6" s="459">
         <f>J32*'Balance sheet'!J32</f>
-        <v>411.24029152158619</v>
+        <v>381.85113920197176</v>
       </c>
       <c r="K6" s="459">
         <f>K32*'Balance sheet'!K32</f>
-        <v>411.56747723603496</v>
+        <v>381.96571354296151</v>
       </c>
       <c r="L6" s="460">
         <f>L32*'Balance sheet'!L32</f>
-        <v>436.83600390913529</v>
+        <v>405.22120260859771</v>
       </c>
       <c r="M6" s="23"/>
       <c r="N6" s="23"/>
@@ -19355,23 +19356,23 @@
       </c>
       <c r="H7" s="36">
         <f t="shared" ref="H7:L7" si="0">H33*H3</f>
-        <v>246.36676319999998</v>
+        <v>254.01909320000001</v>
       </c>
       <c r="I7" s="36">
         <f t="shared" si="0"/>
-        <v>280.96367538666664</v>
+        <v>290.72751247466664</v>
       </c>
       <c r="J7" s="36">
         <f t="shared" si="0"/>
-        <v>287.5512524042</v>
+        <v>301.02773912303331</v>
       </c>
       <c r="K7" s="36">
         <f t="shared" si="0"/>
-        <v>301.18807429029266</v>
+        <v>311.78058339694786</v>
       </c>
       <c r="L7" s="159">
         <f t="shared" si="0"/>
-        <v>314.46687131815565</v>
+        <v>319.62670484646031</v>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="23"/>
@@ -19442,23 +19443,23 @@
       </c>
       <c r="H9" s="36">
         <f t="shared" ref="H9:L9" si="1">H35*H4</f>
-        <v>360.69570575572175</v>
+        <v>335.74871225572161</v>
       </c>
       <c r="I9" s="36">
         <f t="shared" si="1"/>
-        <v>414.16640236648169</v>
+        <v>384.7635174822517</v>
       </c>
       <c r="J9" s="36">
         <f t="shared" si="1"/>
-        <v>430.62832430980291</v>
+        <v>399.85361259696282</v>
       </c>
       <c r="K9" s="36">
         <f t="shared" si="1"/>
-        <v>447.98259561271328</v>
+        <v>415.76169462463071</v>
       </c>
       <c r="L9" s="159">
         <f t="shared" si="1"/>
-        <v>466.28407304661039</v>
+        <v>432.53804893903646</v>
       </c>
       <c r="M9" s="23"/>
       <c r="N9" s="23"/>
@@ -19618,23 +19619,23 @@
       </c>
       <c r="H13" s="246">
         <f t="shared" ref="H13" si="4">SUM(H4:H12)</f>
-        <v>12764.116664286574</v>
+        <v>12127.92680952607</v>
       </c>
       <c r="I13" s="246">
         <f t="shared" ref="I13" si="5">SUM(I4:I12)</f>
-        <v>14153.473357599125</v>
+        <v>13396.913630909894</v>
       </c>
       <c r="J13" s="246">
         <f t="shared" ref="J13:K13" si="6">SUM(J4:J12)</f>
-        <v>14808.784009476432</v>
+        <v>14004.654020973672</v>
       </c>
       <c r="K13" s="246">
         <f t="shared" si="6"/>
-        <v>15455.5762585921</v>
+        <v>14598.020647310223</v>
       </c>
       <c r="L13" s="462">
         <f t="shared" ref="L13" si="7">SUM(L4:L12)</f>
-        <v>16158.596204442341</v>
+        <v>15240.628814461656</v>
       </c>
       <c r="M13" s="23"/>
       <c r="N13" s="23"/>
@@ -19741,23 +19742,23 @@
       </c>
       <c r="H16" s="23">
         <f ca="1">H42*('Balance sheet'!H30+'Balance sheet'!H26)</f>
-        <v>-169.55512513709436</v>
+        <v>-173.6526961074396</v>
       </c>
       <c r="I16" s="23">
         <f ca="1">I42*('Balance sheet'!I30+'Balance sheet'!I26)</f>
-        <v>-195.51963529091284</v>
+        <v>-204.66866963574506</v>
       </c>
       <c r="J16" s="23">
         <f ca="1">J42*('Balance sheet'!J30+'Balance sheet'!J26)</f>
-        <v>-219.27233840034125</v>
+        <v>-234.68611959057748</v>
       </c>
       <c r="K16" s="23">
         <f ca="1">K42*('Balance sheet'!K30+'Balance sheet'!K26)</f>
-        <v>-242.92344650578491</v>
+        <v>-263.89239907938708</v>
       </c>
       <c r="L16" s="158">
         <f ca="1">L42*('Balance sheet'!L30+'Balance sheet'!L26)</f>
-        <v>-266.06498345896733</v>
+        <v>-291.15131847789979</v>
       </c>
       <c r="M16" s="23"/>
       <c r="N16" s="23"/>
@@ -19792,23 +19793,23 @@
       </c>
       <c r="H17" s="246">
         <f ca="1">H3-H13+H14+H15+H16</f>
-        <v>13845.324210576331</v>
+        <v>15309.191494366491</v>
       </c>
       <c r="I17" s="246">
         <f ca="1">I3-I13+I14+I15+I16</f>
-        <v>16190.536940443291</v>
+        <v>17999.234272787689</v>
       </c>
       <c r="J17" s="246">
         <f ca="1">J3-J13+J14+J15+J16</f>
-        <v>16227.514565623225</v>
+        <v>18481.066285852419</v>
       </c>
       <c r="K17" s="246">
         <f t="shared" ref="K17:L17" ca="1" si="9">K3-K13+K14+K15+K16</f>
-        <v>17039.334456890447</v>
+        <v>19027.28080110472</v>
       </c>
       <c r="L17" s="462">
         <f t="shared" ca="1" si="9"/>
-        <v>17756.52047711561</v>
+        <v>19210.253002545262</v>
       </c>
       <c r="M17" s="23"/>
       <c r="N17" s="23"/>
@@ -19837,23 +19838,23 @@
       </c>
       <c r="H18" s="456">
         <f ca="1">H17*H44</f>
-        <v>-4568.9569894901897</v>
+        <v>-5052.0331931409419</v>
       </c>
       <c r="I18" s="456">
         <f t="shared" ref="I18:L18" ca="1" si="10">I17*I44</f>
-        <v>-5342.8771903462866</v>
+        <v>-5939.7473100199377</v>
       </c>
       <c r="J18" s="456">
         <f t="shared" ca="1" si="10"/>
-        <v>-5355.0798066556645</v>
+        <v>-6098.7518743312985</v>
       </c>
       <c r="K18" s="456">
         <f t="shared" ca="1" si="10"/>
-        <v>-5622.9803707738474</v>
+        <v>-6279.0026643645579</v>
       </c>
       <c r="L18" s="457">
         <f t="shared" ca="1" si="10"/>
-        <v>-5859.6517574481513</v>
+        <v>-6339.3834908399367</v>
       </c>
       <c r="M18" s="23"/>
       <c r="N18" s="23"/>
@@ -19933,23 +19934,23 @@
       </c>
       <c r="H20" s="246">
         <f t="shared" ref="H20" ca="1" si="13">SUM(H17:H19)</f>
-        <v>9456.2005544194744</v>
+        <v>10436.991634558883</v>
       </c>
       <c r="I20" s="246">
         <f t="shared" ref="I20" ca="1" si="14">SUM(I17:I19)</f>
-        <v>11027.49308343034</v>
+        <v>12239.320296101085</v>
       </c>
       <c r="J20" s="246">
         <f t="shared" ref="J20:K20" ca="1" si="15">SUM(J17:J19)</f>
-        <v>11052.268092300894</v>
+        <v>12562.147744854456</v>
       </c>
       <c r="K20" s="246">
         <f t="shared" ca="1" si="15"/>
-        <v>11596.187419449934</v>
+        <v>12928.111470073496</v>
       </c>
       <c r="L20" s="462">
         <f t="shared" ref="L20" ca="1" si="16">SUM(L17:L19)</f>
-        <v>12076.702053000792</v>
+        <v>13050.702845038659</v>
       </c>
       <c r="M20" s="23"/>
       <c r="N20" s="23"/>
@@ -20024,23 +20025,23 @@
       </c>
       <c r="H22" s="246">
         <f t="shared" ca="1" si="17"/>
-        <v>9456.2005544194744</v>
+        <v>10436.991634558883</v>
       </c>
       <c r="I22" s="246">
         <f t="shared" ca="1" si="17"/>
-        <v>11027.49308343034</v>
+        <v>12239.320296101085</v>
       </c>
       <c r="J22" s="246">
         <f t="shared" ca="1" si="17"/>
-        <v>11052.268092300894</v>
+        <v>12562.147744854456</v>
       </c>
       <c r="K22" s="246">
         <f t="shared" ca="1" si="17"/>
-        <v>11596.187419449934</v>
+        <v>12928.111470073496</v>
       </c>
       <c r="L22" s="462">
         <f t="shared" ca="1" si="17"/>
-        <v>12076.702053000792</v>
+        <v>13050.702845038659</v>
       </c>
       <c r="M22" s="23"/>
       <c r="N22" s="23"/>
@@ -20069,23 +20070,23 @@
       </c>
       <c r="H23" s="459">
         <f ca="1">H49*H17</f>
-        <v>-5.2879191136485089</v>
+        <v>-5.8470112426638456</v>
       </c>
       <c r="I23" s="459">
         <f ca="1">I49*I17</f>
-        <v>-6.1836218816892918</v>
+        <v>-6.8744143145023111</v>
       </c>
       <c r="J23" s="459">
         <f ca="1">J49*J17</f>
-        <v>-6.1977446778038772</v>
+        <v>-7.0584395256639541</v>
       </c>
       <c r="K23" s="459">
         <f ca="1">K49*K17</f>
-        <v>-6.507801550043296</v>
+        <v>-7.2670542270191252</v>
       </c>
       <c r="L23" s="460">
         <f ca="1">L49*L17</f>
-        <v>-6.7817150826345474</v>
+        <v>-7.3369364621006756</v>
       </c>
       <c r="M23" s="23"/>
       <c r="N23" s="23"/>
@@ -20115,23 +20116,23 @@
       </c>
       <c r="H24" s="250">
         <f t="shared" ref="H24:L24" ca="1" si="18">H20+H21+H23</f>
-        <v>9450.9126353058255</v>
+        <v>10431.144623316219</v>
       </c>
       <c r="I24" s="250">
         <f t="shared" ca="1" si="18"/>
-        <v>11021.30946154865</v>
+        <v>12232.445881786582</v>
       </c>
       <c r="J24" s="250">
         <f t="shared" ca="1" si="18"/>
-        <v>11046.07034762309</v>
+        <v>12555.089305328791</v>
       </c>
       <c r="K24" s="250">
         <f t="shared" ca="1" si="18"/>
-        <v>11589.67961789989</v>
+        <v>12920.844415846477</v>
       </c>
       <c r="L24" s="583">
         <f t="shared" ca="1" si="18"/>
-        <v>12069.920337918158</v>
+        <v>13043.365908576558</v>
       </c>
       <c r="M24" s="23"/>
       <c r="N24" s="23"/>
@@ -20993,23 +20994,23 @@
       </c>
       <c r="H4" s="231">
         <f ca="1">'Cash flow'!C59</f>
-        <v>8732.2556152478992</v>
+        <v>9858.2487019969321</v>
       </c>
       <c r="I4" s="231">
         <f ca="1">'Cash flow'!D59</f>
-        <v>13016.200864995011</v>
+        <v>15649.9030308865</v>
       </c>
       <c r="J4" s="231">
         <f ca="1">'Cash flow'!E59</f>
-        <v>16155.84962243522</v>
+        <v>20673.133169540255</v>
       </c>
       <c r="K4" s="231">
         <f ca="1">'Cash flow'!F59</f>
-        <v>19265.750871146549</v>
+        <v>25403.827130578902</v>
       </c>
       <c r="L4" s="233">
         <f ca="1">'Cash flow'!G59</f>
-        <v>22338.55600344397</v>
+        <v>29694.201437450287</v>
       </c>
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
@@ -21038,23 +21039,23 @@
       </c>
       <c r="H5" s="463">
         <f>H55*'Income statement'!H3</f>
-        <v>1338.9498000000001</v>
+        <v>1380.5385500000002</v>
       </c>
       <c r="I5" s="463">
         <f>I55*'Income statement'!I3</f>
-        <v>1526.9764966666664</v>
+        <v>1580.0408286666666</v>
       </c>
       <c r="J5" s="463">
         <f>J55*'Income statement'!J3</f>
-        <v>1562.778545675</v>
+        <v>1636.0203213208333</v>
       </c>
       <c r="K5" s="463">
         <f>K55*'Income statement'!K3</f>
-        <v>1636.8917080994167</v>
+        <v>1694.4596923747167</v>
       </c>
       <c r="L5" s="464">
         <f>L55*'Income statement'!L3</f>
-        <v>1709.059083250846</v>
+        <v>1737.1016567742408</v>
       </c>
       <c r="M5" s="23"/>
       <c r="N5" s="23" t="s">
@@ -21127,23 +21128,23 @@
       </c>
       <c r="H7" s="463">
         <f>Schedules!H10</f>
-        <v>1517.011992493952</v>
+        <v>1440.7713122218427</v>
       </c>
       <c r="I7" s="463">
         <f>Schedules!I10</f>
-        <v>1710.2038708413002</v>
+        <v>1620.3455099315495</v>
       </c>
       <c r="J7" s="463">
         <f>Schedules!J10</f>
-        <v>1759.5709281857303</v>
+        <v>1665.520117767835</v>
       </c>
       <c r="K7" s="463">
         <f>Schedules!K10</f>
-        <v>1811.762653742217</v>
+        <v>1713.2921342260404</v>
       </c>
       <c r="L7" s="464">
         <f>Schedules!L10</f>
-        <v>1866.9469597049247</v>
+        <v>1763.815500820293</v>
       </c>
       <c r="M7" s="23"/>
       <c r="N7" s="23" t="s">
@@ -21174,23 +21175,23 @@
       </c>
       <c r="H8" s="231">
         <f>Schedules!H18</f>
-        <v>1043.1801210350143</v>
+        <v>971.03008630070963</v>
       </c>
       <c r="I8" s="231">
         <f>Schedules!I18</f>
-        <v>1197.8245120608817</v>
+        <v>1112.7874447410884</v>
       </c>
       <c r="J8" s="231">
         <f>Schedules!J18</f>
-        <v>1245.43458739938</v>
+        <v>1156.4300138013787</v>
       </c>
       <c r="K8" s="231">
         <f>Schedules!K18</f>
-        <v>1295.6254561825674</v>
+        <v>1202.4383101859671</v>
       </c>
       <c r="L8" s="233">
         <f>Schedules!L18</f>
-        <v>1348.5557715147438</v>
+        <v>1250.9577659071292</v>
       </c>
       <c r="M8" s="23"/>
       <c r="N8" s="23" t="s">
@@ -21261,23 +21262,23 @@
       </c>
       <c r="H10" s="231">
         <f>H60*'Income statement'!H3</f>
-        <v>1338.9498000000001</v>
+        <v>1380.5385500000002</v>
       </c>
       <c r="I10" s="231">
         <f>I60*'Income statement'!I3</f>
-        <v>1526.9764966666664</v>
+        <v>1580.0408286666666</v>
       </c>
       <c r="J10" s="231">
         <f>J60*'Income statement'!J3</f>
-        <v>1562.778545675</v>
+        <v>1636.0203213208333</v>
       </c>
       <c r="K10" s="231">
         <f>K60*'Income statement'!K3</f>
-        <v>1636.8917080994167</v>
+        <v>1694.4596923747167</v>
       </c>
       <c r="L10" s="233">
         <f>L60*'Income statement'!L3</f>
-        <v>1709.059083250846</v>
+        <v>1737.1016567742408</v>
       </c>
       <c r="M10" s="23"/>
       <c r="N10" s="23" t="s">
@@ -21354,23 +21355,23 @@
       </c>
       <c r="H12" s="235">
         <f t="shared" ca="1" si="0"/>
-        <v>14970.347328776867</v>
+        <v>16031.127200519484</v>
       </c>
       <c r="I12" s="235">
         <f t="shared" ca="1" si="0"/>
-        <v>20478.182241230526</v>
+        <v>23043.117642892474</v>
       </c>
       <c r="J12" s="235">
         <f t="shared" ca="1" si="0"/>
-        <v>24286.412229370329</v>
+        <v>28767.123943751136</v>
       </c>
       <c r="K12" s="235">
         <f t="shared" ca="1" si="0"/>
-        <v>28146.922397270169</v>
+        <v>34208.476959740343</v>
       </c>
       <c r="L12" s="237">
         <f t="shared" ca="1" si="0"/>
-        <v>31972.17690116533</v>
+        <v>39183.17801772619</v>
       </c>
       <c r="M12" s="23"/>
       <c r="N12" s="23"/>
@@ -21399,23 +21400,23 @@
       </c>
       <c r="H13" s="231">
         <f>Schedules!H44</f>
-        <v>37039.735444846156</v>
+        <v>36884.761697346155</v>
       </c>
       <c r="I13" s="231">
         <f>Schedules!I44</f>
-        <v>39612.587338334903</v>
+        <v>39274.959305948018</v>
       </c>
       <c r="J13" s="231">
         <f>Schedules!J44</f>
-        <v>42287.702686320044</v>
+        <v>41758.898414504903</v>
       </c>
       <c r="K13" s="231">
         <f>Schedules!K44</f>
-        <v>45070.624871186898</v>
+        <v>44341.660456870035</v>
       </c>
       <c r="L13" s="233">
         <f>Schedules!L44</f>
-        <v>47967.238052234025</v>
+        <v>47028.63924573375</v>
       </c>
       <c r="M13" s="23"/>
       <c r="N13" s="23" t="s">
@@ -21446,23 +21447,23 @@
       </c>
       <c r="H14" s="463">
         <f>Schedules!H46</f>
-        <v>3447.2083766863848</v>
+        <v>3208.7872266863837</v>
       </c>
       <c r="I14" s="463">
         <f>Schedules!I46</f>
-        <v>3958.233682290384</v>
+        <v>3677.2270901567176</v>
       </c>
       <c r="J14" s="463">
         <f>Schedules!J46</f>
-        <v>4115.562073823291</v>
+        <v>3821.4447823952155</v>
       </c>
       <c r="K14" s="463">
         <f>Schedules!K46</f>
-        <v>4281.4187459490076</v>
+        <v>3973.4800651771229</v>
       </c>
       <c r="L14" s="464">
         <f>Schedules!L46</f>
-        <v>4456.3279708417303</v>
+        <v>4133.813521328786</v>
       </c>
       <c r="M14" s="23"/>
       <c r="N14" s="23" t="s">
@@ -21674,23 +21675,23 @@
       </c>
       <c r="H19" s="231">
         <f>H69*H32</f>
-        <v>1544.5723864444976</v>
+        <v>1437.7442854440205</v>
       </c>
       <c r="I19" s="231">
         <f t="shared" ref="I19:L19" si="2">I69*I32</f>
-        <v>1773.5447865896331</v>
+        <v>1647.6356522437288</v>
       </c>
       <c r="J19" s="231">
         <f t="shared" si="2"/>
-        <v>1844.0380851116804</v>
+        <v>1712.2545092222722</v>
       </c>
       <c r="K19" s="231">
         <f t="shared" si="2"/>
-        <v>1918.3526051173471</v>
+        <v>1780.3761525607999</v>
       </c>
       <c r="L19" s="233">
         <f t="shared" si="2"/>
-        <v>1996.723254460976</v>
+        <v>1852.2159144591269</v>
       </c>
       <c r="M19" s="23"/>
       <c r="N19" s="23"/>
@@ -21725,23 +21726,23 @@
       </c>
       <c r="H20" s="239">
         <f t="shared" ca="1" si="3"/>
-        <v>61556.107678011329</v>
+        <v>62116.664551253474</v>
       </c>
       <c r="I20" s="239">
         <f t="shared" ca="1" si="3"/>
-        <v>70547.109370501217</v>
+        <v>72367.501013296715</v>
       </c>
       <c r="J20" s="239">
         <f t="shared" ca="1" si="3"/>
-        <v>77252.886950798784</v>
+        <v>80778.893526046973</v>
       </c>
       <c r="K20" s="239">
         <f t="shared" ca="1" si="3"/>
-        <v>84131.658979148371</v>
+        <v>89018.33399397324</v>
       </c>
       <c r="L20" s="241">
         <f t="shared" ca="1" si="3"/>
-        <v>91102.534461183401</v>
+        <v>96907.914981729191</v>
       </c>
       <c r="M20" s="23"/>
       <c r="N20" s="23"/>
@@ -21786,23 +21787,23 @@
       </c>
       <c r="H22" s="231">
         <f>H72*'Income statement'!H3</f>
-        <v>963.94462640610516</v>
+        <v>993.88544426309056</v>
       </c>
       <c r="I22" s="231">
         <f>I72*'Income statement'!I3</f>
-        <v>1099.3099133442142</v>
+        <v>1137.5122997856101</v>
       </c>
       <c r="J22" s="231">
         <f>J72*'Income statement'!J3</f>
-        <v>1125.0847353397151</v>
+        <v>1177.8133858553972</v>
       </c>
       <c r="K22" s="231">
         <f>K72*'Income statement'!K3</f>
-        <v>1178.4407197574872</v>
+        <v>1219.8854020713472</v>
       </c>
       <c r="L22" s="233">
         <f>L72*'Income statement'!L3</f>
-        <v>1230.3958815410388</v>
+        <v>1250.5844562422519</v>
       </c>
       <c r="M22" s="23"/>
       <c r="N22" s="23" t="s">
@@ -21833,23 +21834,23 @@
       </c>
       <c r="H23" s="463">
         <f>H73*'Income statement'!H9</f>
-        <v>847.9181774048119</v>
+        <v>789.27315080009953</v>
       </c>
       <c r="I23" s="463">
         <f>I73*'Income statement'!I9</f>
-        <v>973.6163071337711</v>
+        <v>904.49643638497912</v>
       </c>
       <c r="J23" s="463">
         <f>J73*'Income statement'!J9</f>
-        <v>1012.3147519115262</v>
+        <v>939.97001076458798</v>
       </c>
       <c r="K23" s="463">
         <f>K73*'Income statement'!K9</f>
-        <v>1053.1109184822421</v>
+        <v>977.36649678774438</v>
       </c>
       <c r="L23" s="464">
         <f>L73*'Income statement'!L9</f>
-        <v>1096.1337633399376</v>
+        <v>1016.8041045739653</v>
       </c>
       <c r="M23" s="23"/>
       <c r="N23" s="23"/>
@@ -21878,23 +21879,23 @@
       </c>
       <c r="H24" s="231">
         <f ca="1">H74*'Income statement'!H18</f>
-        <v>1063.8257302229667</v>
+        <v>1176.3041134260097</v>
       </c>
       <c r="I24" s="231">
         <f ca="1">I74*'Income statement'!I18</f>
-        <v>1244.0235794703742</v>
+        <v>1382.9974836613485</v>
       </c>
       <c r="J24" s="231">
         <f ca="1">J74*'Income statement'!J18</f>
-        <v>1246.8648093694114</v>
+        <v>1420.0197509154318</v>
       </c>
       <c r="K24" s="231">
         <f ca="1">K74*'Income statement'!K18</f>
-        <v>1309.2421777503669</v>
+        <v>1461.9889418645887</v>
       </c>
       <c r="L24" s="233">
         <f ca="1">L74*'Income statement'!L18</f>
-        <v>1364.3482142770463</v>
+        <v>1476.0478785025114</v>
       </c>
       <c r="M24" s="23"/>
       <c r="N24" s="23"/>
@@ -22007,23 +22008,23 @@
       </c>
       <c r="H27" s="463">
         <f>H77*'Income statement'!H4</f>
-        <v>2697.1094431600736</v>
+        <v>2510.5677941367517</v>
       </c>
       <c r="I27" s="463">
         <f>I77*'Income statement'!I4</f>
-        <v>3096.9376597424393</v>
+        <v>2877.076992670588</v>
       </c>
       <c r="J27" s="463">
         <f>J77*'Income statement'!J4</f>
-        <v>3220.0320143948479</v>
+        <v>2989.9134844352957</v>
       </c>
       <c r="K27" s="463">
         <f>K77*'Income statement'!K4</f>
-        <v>3349.798929451887</v>
+        <v>3108.8664899042483</v>
       </c>
       <c r="L27" s="464">
         <f>L77*'Income statement'!L4</f>
-        <v>3486.6485975324222</v>
+        <v>3234.312018978073</v>
       </c>
       <c r="M27" s="23"/>
       <c r="N27" s="23" t="s">
@@ -22100,23 +22101,23 @@
       </c>
       <c r="H29" s="235">
         <f t="shared" ref="H29:L29" ca="1" si="5">SUM(H22:H28)</f>
-        <v>5668.7979771939572</v>
+        <v>5566.0305026259521</v>
       </c>
       <c r="I29" s="235">
         <f t="shared" ca="1" si="5"/>
-        <v>6490.887459690799</v>
+        <v>6379.0832125025254</v>
       </c>
       <c r="J29" s="235">
         <f t="shared" ca="1" si="5"/>
-        <v>6675.2963110155006</v>
+        <v>6598.7166319707121</v>
       </c>
       <c r="K29" s="235">
         <f t="shared" ca="1" si="5"/>
-        <v>6936.5927454419834</v>
+        <v>6814.1073306279286</v>
       </c>
       <c r="L29" s="237">
         <f t="shared" ca="1" si="5"/>
-        <v>7429.5264566904443</v>
+        <v>7229.7484582968018</v>
       </c>
       <c r="M29" s="23"/>
       <c r="N29" s="23"/>
@@ -22145,23 +22146,23 @@
       </c>
       <c r="H30" s="231">
         <f ca="1">H80*H44</f>
-        <v>5846.7284530032539</v>
+        <v>5988.0240037048134</v>
       </c>
       <c r="I30" s="231">
         <f ca="1">I80*I44</f>
-        <v>6742.0563893418221</v>
+        <v>7057.5403322670709</v>
       </c>
       <c r="J30" s="231">
         <f ca="1">J80*J44</f>
-        <v>7561.1151172531463</v>
+        <v>8092.6248134681882</v>
       </c>
       <c r="K30" s="231">
         <f ca="1">K80*K44</f>
-        <v>8376.6705691649968</v>
+        <v>9099.7378992892081</v>
       </c>
       <c r="L30" s="233">
         <f ca="1">L80*L44</f>
-        <v>9174.6546020333553</v>
+        <v>10039.700637168959</v>
       </c>
       <c r="M30" s="23"/>
       <c r="N30" s="23" t="s">
@@ -22236,23 +22237,23 @@
       </c>
       <c r="H32" s="231">
         <f>Schedules!H35</f>
-        <v>6726.2602471929467</v>
+        <v>6261.0482471929445</v>
       </c>
       <c r="I32" s="231">
         <f>Schedules!I35</f>
-        <v>7723.3827947129457</v>
+        <v>7175.0772490862792</v>
       </c>
       <c r="J32" s="231">
         <f>Schedules!J35</f>
-        <v>8030.3650220942263</v>
+        <v>7456.4776241857871</v>
       </c>
       <c r="K32" s="231">
         <f>Schedules!K35</f>
-        <v>8353.9877969736754</v>
+        <v>7753.1318344919482</v>
       </c>
       <c r="L32" s="233">
         <f>Schedules!L35</f>
-        <v>8695.274089447279</v>
+        <v>8065.977602592754</v>
       </c>
       <c r="M32" s="23"/>
       <c r="N32" s="23" t="s">
@@ -22283,23 +22284,23 @@
       </c>
       <c r="H33" s="463">
         <f>H83*'Income statement'!H3</f>
-        <v>2410.1096399999997</v>
+        <v>2484.9693899999997</v>
       </c>
       <c r="I33" s="463">
         <f>I83*'Income statement'!I3</f>
-        <v>2748.5576939999992</v>
+        <v>2844.0734915999997</v>
       </c>
       <c r="J33" s="463">
         <f>J83*'Income statement'!J3</f>
-        <v>2813.0013822149999</v>
+        <v>2944.8365783774998</v>
       </c>
       <c r="K33" s="463">
         <f>K83*'Income statement'!K3</f>
-        <v>2946.40507457895</v>
+        <v>3050.0274462744896</v>
       </c>
       <c r="L33" s="464">
         <f>L83*'Income statement'!L3</f>
-        <v>3076.3063498515226</v>
+        <v>3126.7829821936334</v>
       </c>
       <c r="M33" s="23"/>
       <c r="N33" s="23" t="s">
@@ -22330,23 +22331,23 @@
       </c>
       <c r="H34" s="231">
         <f>H84*'Income statement'!H9</f>
-        <v>598.64156400295178</v>
+        <v>557.23739154483633</v>
       </c>
       <c r="I34" s="231">
         <f>I84*'Income statement'!I9</f>
-        <v>687.38612329934392</v>
+        <v>638.58657089986275</v>
       </c>
       <c r="J34" s="231">
         <f>J84*'Income statement'!J9</f>
-        <v>714.70774244087704</v>
+        <v>663.63138844626815</v>
       </c>
       <c r="K34" s="231">
         <f>K84*'Income statement'!K9</f>
-        <v>743.51038120015767</v>
+        <v>690.03380730894207</v>
       </c>
       <c r="L34" s="233">
         <f>L84*'Income statement'!L9</f>
-        <v>773.88508458521198</v>
+        <v>717.87728541190859</v>
       </c>
       <c r="M34" s="23"/>
       <c r="N34" s="23"/>
@@ -22422,23 +22423,23 @@
       </c>
       <c r="H36" s="231">
         <f>H86*'Income statement'!H3</f>
-        <v>380.38010992986017</v>
+        <v>392.19499148617058</v>
       </c>
       <c r="I36" s="231">
         <f>I86*'Income statement'!I3</f>
-        <v>433.79631384416302</v>
+        <v>448.87127516049816</v>
       </c>
       <c r="J36" s="231">
         <f>J86*'Income statement'!J3</f>
-        <v>443.96726075905423</v>
+        <v>464.77439981058569</v>
       </c>
       <c r="K36" s="231">
         <f>K86*'Income statement'!K3</f>
-        <v>465.0219506886163</v>
+        <v>481.37634738599741</v>
       </c>
       <c r="L36" s="233">
         <f>L86*'Income statement'!L3</f>
-        <v>485.5238650198707</v>
+        <v>493.49043493873177</v>
       </c>
       <c r="M36" s="23"/>
       <c r="N36" s="23" t="s">
@@ -22475,23 +22476,23 @@
       </c>
       <c r="H37" s="239">
         <f t="shared" ca="1" si="6"/>
-        <v>22392.917991322971</v>
+        <v>22011.504526554712</v>
       </c>
       <c r="I37" s="239">
         <f t="shared" ca="1" si="6"/>
-        <v>25415.066774889074</v>
+        <v>25132.232131516237</v>
       </c>
       <c r="J37" s="239">
         <f t="shared" ca="1" si="6"/>
-        <v>26660.452835777804</v>
+        <v>26643.061436259046</v>
       </c>
       <c r="K37" s="239">
         <f t="shared" ca="1" si="6"/>
-        <v>28102.188518048381</v>
+        <v>28168.414665378514</v>
       </c>
       <c r="L37" s="241">
         <f t="shared" ca="1" si="6"/>
-        <v>29753.170447627683</v>
+        <v>29791.577400602786</v>
       </c>
       <c r="M37" s="23"/>
       <c r="N37" s="23"/>
@@ -22578,23 +22579,23 @@
       </c>
       <c r="H40" s="463">
         <f>+-'Changes in Equity'!H28</f>
-        <v>-327.77899600000001</v>
+        <v>-328.610771</v>
       </c>
       <c r="I40" s="463">
         <f>+-'Changes in Equity'!I28</f>
-        <v>-388.85805586666663</v>
+        <v>-391.81240414666667</v>
       </c>
       <c r="J40" s="463">
         <f>+-'Changes in Equity'!J28</f>
-        <v>-451.36919769366665</v>
+        <v>-457.25321699950001</v>
       </c>
       <c r="K40" s="463">
         <f>+-'Changes in Equity'!K28</f>
-        <v>-516.84486601764331</v>
+        <v>-525.03160469448869</v>
       </c>
       <c r="L40" s="464">
         <f>+-'Changes in Equity'!L28</f>
-        <v>-619.38841101269406</v>
+        <v>-629.2577041009431</v>
       </c>
       <c r="M40" s="23"/>
       <c r="N40" s="23" t="s">
@@ -22625,23 +22626,23 @@
       </c>
       <c r="H41" s="231">
         <f>+'Changes in Equity'!H37</f>
-        <v>27641.945179999999</v>
+        <v>27604.515305000001</v>
       </c>
       <c r="I41" s="231">
         <f>+'Changes in Equity'!I37</f>
-        <v>26267.666333000001</v>
+        <v>26182.478559200001</v>
       </c>
       <c r="J41" s="231">
         <f>+'Changes in Equity'!J37</f>
-        <v>24861.165641892501</v>
+        <v>24710.06027001125</v>
       </c>
       <c r="K41" s="231">
         <f>+'Changes in Equity'!K37</f>
-        <v>23387.963104603026</v>
+        <v>23185.046546874004</v>
       </c>
       <c r="L41" s="233">
         <f>+'Changes in Equity'!L37</f>
-        <v>21849.809929677263</v>
+        <v>21621.655055777188</v>
       </c>
       <c r="M41" s="23"/>
       <c r="N41" s="23" t="s">
@@ -22719,23 +22720,23 @@
       </c>
       <c r="H43" s="231">
         <f ca="1">+'Changes in Equity'!H21</f>
-        <v>9767.0235026883638</v>
+        <v>10747.255490698757</v>
       </c>
       <c r="I43" s="231">
         <f ca="1">+'Changes in Equity'!I21</f>
-        <v>17171.234318478815</v>
+        <v>19362.602726727138</v>
       </c>
       <c r="J43" s="231">
         <f ca="1">+'Changes in Equity'!J21</f>
-        <v>24100.637670822147</v>
+        <v>27801.025036776173</v>
       </c>
       <c r="K43" s="231">
         <f ca="1">+'Changes in Equity'!K21</f>
-        <v>31076.352222514601</v>
+        <v>36107.904386415212</v>
       </c>
       <c r="L43" s="233">
         <f ca="1">+'Changes in Equity'!L21</f>
-        <v>38036.94249489114</v>
+        <v>44041.940229450156</v>
       </c>
       <c r="M43" s="23"/>
       <c r="N43" s="23" t="s">
@@ -22772,23 +22773,23 @@
       </c>
       <c r="H44" s="466">
         <f t="shared" ref="H44" ca="1" si="9">+H39+H40+H41+H42+H43</f>
-        <v>38978.189686688362</v>
+        <v>39920.160024698758</v>
       </c>
       <c r="I44" s="466">
         <f t="shared" ref="I44" ca="1" si="10">+I39+I40+I41+I42+I43</f>
-        <v>44947.042595612147</v>
+        <v>47050.268881780474</v>
       </c>
       <c r="J44" s="466">
         <f t="shared" ref="J44" ca="1" si="11">+J39+J40+J41+J42+J43</f>
-        <v>50407.43411502098</v>
+        <v>53950.832089787924</v>
       </c>
       <c r="K44" s="466">
         <f t="shared" ref="K44" ca="1" si="12">+K39+K40+K41+K42+K43</f>
-        <v>55844.470461099983</v>
+        <v>60664.919328594726</v>
       </c>
       <c r="L44" s="467">
         <f t="shared" ref="L44" ca="1" si="13">+L39+L40+L41+L42+L43</f>
-        <v>61164.364013555707</v>
+        <v>66931.337581126398</v>
       </c>
       <c r="M44" s="23"/>
       <c r="N44" s="23"/>
@@ -22905,23 +22906,23 @@
       </c>
       <c r="H47" s="235">
         <f t="shared" ca="1" si="14"/>
-        <v>39163.189686688362</v>
+        <v>40105.160024698758</v>
       </c>
       <c r="I47" s="235">
         <f t="shared" ca="1" si="14"/>
-        <v>45132.042595612147</v>
+        <v>47235.268881780474</v>
       </c>
       <c r="J47" s="235">
         <f t="shared" ca="1" si="14"/>
-        <v>50592.43411502098</v>
+        <v>54135.832089787924</v>
       </c>
       <c r="K47" s="235">
         <f t="shared" ca="1" si="14"/>
-        <v>56029.470461099983</v>
+        <v>60849.919328594726</v>
       </c>
       <c r="L47" s="237">
         <f t="shared" ca="1" si="14"/>
-        <v>61349.364013555707</v>
+        <v>67116.337581126398</v>
       </c>
       <c r="M47" s="23"/>
       <c r="N47" s="23"/>
@@ -22956,23 +22957,23 @@
       </c>
       <c r="H48" s="568">
         <f t="shared" ref="H48:L48" ca="1" si="16">+H37+H47</f>
-        <v>61556.107678011336</v>
+        <v>62116.664551253474</v>
       </c>
       <c r="I48" s="568">
         <f t="shared" ca="1" si="16"/>
-        <v>70547.109370501217</v>
+        <v>72367.501013296715</v>
       </c>
       <c r="J48" s="568">
         <f t="shared" ca="1" si="16"/>
-        <v>77252.886950798784</v>
+        <v>80778.893526046973</v>
       </c>
       <c r="K48" s="568">
         <f t="shared" ca="1" si="16"/>
-        <v>84131.658979148371</v>
+        <v>89018.33399397324</v>
       </c>
       <c r="L48" s="570">
         <f t="shared" ca="1" si="16"/>
-        <v>91102.534461183386</v>
+        <v>96907.914981729176</v>
       </c>
       <c r="M48" s="23"/>
       <c r="N48" s="23"/>
@@ -24240,23 +24241,23 @@
       </c>
       <c r="C2" s="164">
         <f ca="1">+'Income statement'!H24</f>
-        <v>9450.9126353058255</v>
+        <v>10431.144623316219</v>
       </c>
       <c r="D2" s="164">
         <f ca="1">+'Income statement'!I24</f>
-        <v>11021.30946154865</v>
+        <v>12232.445881786582</v>
       </c>
       <c r="E2" s="164">
         <f ca="1">+'Income statement'!J24</f>
-        <v>11046.07034762309</v>
+        <v>12555.089305328791</v>
       </c>
       <c r="F2" s="164">
         <f ca="1">+'Income statement'!K24</f>
-        <v>11589.67961789989</v>
+        <v>12920.844415846477</v>
       </c>
       <c r="G2" s="164">
         <f ca="1">+'Income statement'!L24</f>
-        <v>12069.920337918158</v>
+        <v>13043.365908576558</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" thickBot="1">
@@ -24312,23 +24313,23 @@
       </c>
       <c r="C6" s="36">
         <f>+'Balance sheet'!G5-'Balance sheet'!H5</f>
-        <v>-271.9498000000001</v>
+        <v>-313.53855000000021</v>
       </c>
       <c r="D6" s="36">
         <f>+'Balance sheet'!H5-'Balance sheet'!I5</f>
-        <v>-188.02669666666634</v>
+        <v>-199.50227866666637</v>
       </c>
       <c r="E6" s="36">
         <f>+'Balance sheet'!I5-'Balance sheet'!J5</f>
-        <v>-35.802049008333597</v>
+        <v>-55.979492654166734</v>
       </c>
       <c r="F6" s="36">
         <f>+'Balance sheet'!J5-'Balance sheet'!K5</f>
-        <v>-74.113162424416714</v>
+        <v>-58.439371053883406</v>
       </c>
       <c r="G6" s="159">
         <f>+'Balance sheet'!K5-'Balance sheet'!L5</f>
-        <v>-72.167375151429269</v>
+        <v>-42.641964399524113</v>
       </c>
       <c r="I6" s="15"/>
     </row>
@@ -24371,23 +24372,23 @@
       </c>
       <c r="C8" s="36">
         <f>+'Balance sheet'!G7-'Balance sheet'!H7</f>
-        <v>-5.0119924939519933</v>
+        <v>71.228687778157337</v>
       </c>
       <c r="D8" s="36">
         <f>+'Balance sheet'!H7-'Balance sheet'!I7</f>
-        <v>-193.19187834734817</v>
+        <v>-179.57419770970682</v>
       </c>
       <c r="E8" s="36">
         <f>+'Balance sheet'!I7-'Balance sheet'!J7</f>
-        <v>-49.367057344430123</v>
+        <v>-45.174607836285531</v>
       </c>
       <c r="F8" s="36">
         <f>+'Balance sheet'!J7-'Balance sheet'!K7</f>
-        <v>-52.191725556486745</v>
+        <v>-47.772016458205371</v>
       </c>
       <c r="G8" s="159">
         <f>+'Balance sheet'!K7-'Balance sheet'!L7</f>
-        <v>-55.18430596270764</v>
+        <v>-50.523366594252593</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -24400,23 +24401,23 @@
       </c>
       <c r="C9" s="459">
         <f>+'Balance sheet'!G8-'Balance sheet'!H8</f>
-        <v>133.81987896498572</v>
+        <v>205.96991369929037</v>
       </c>
       <c r="D9" s="459">
         <f>+'Balance sheet'!H8-'Balance sheet'!I8</f>
-        <v>-154.64439102586744</v>
+        <v>-141.75735844037877</v>
       </c>
       <c r="E9" s="459">
         <f>+'Balance sheet'!I8-'Balance sheet'!J8</f>
-        <v>-47.610075338498291</v>
+        <v>-43.64256906029027</v>
       </c>
       <c r="F9" s="459">
         <f>+'Balance sheet'!J8-'Balance sheet'!K8</f>
-        <v>-50.190868783187398</v>
+        <v>-46.008296384588448</v>
       </c>
       <c r="G9" s="460">
         <f>+'Balance sheet'!K8-'Balance sheet'!L8</f>
-        <v>-52.930315332176406</v>
+        <v>-48.519455721162103</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -24458,23 +24459,23 @@
       </c>
       <c r="C11" s="459">
         <f>+'Balance sheet'!G10-'Balance sheet'!H10</f>
-        <v>-269.9498000000001</v>
+        <v>-311.53855000000021</v>
       </c>
       <c r="D11" s="459">
         <f>+'Balance sheet'!H10-'Balance sheet'!I10</f>
-        <v>-188.02669666666634</v>
+        <v>-199.50227866666637</v>
       </c>
       <c r="E11" s="459">
         <f>+'Balance sheet'!I10-'Balance sheet'!J10</f>
-        <v>-35.802049008333597</v>
+        <v>-55.979492654166734</v>
       </c>
       <c r="F11" s="459">
         <f>+'Balance sheet'!J10-'Balance sheet'!K10</f>
-        <v>-74.113162424416714</v>
+        <v>-58.439371053883406</v>
       </c>
       <c r="G11" s="460">
         <f>+'Balance sheet'!K10-'Balance sheet'!L10</f>
-        <v>-72.167375151429269</v>
+        <v>-42.641964399524113</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -24527,23 +24528,23 @@
       </c>
       <c r="C14" s="36">
         <f>+'Balance sheet'!G13-'Balance sheet'!H13</f>
-        <v>-3729.7354448461556</v>
+        <v>-3574.7616973461554</v>
       </c>
       <c r="D14" s="36">
         <f>+'Balance sheet'!H13-'Balance sheet'!I13</f>
-        <v>-2572.851893488747</v>
+        <v>-2390.1976086018622</v>
       </c>
       <c r="E14" s="36">
         <f>+'Balance sheet'!I13-'Balance sheet'!J13</f>
-        <v>-2675.1153479851419</v>
+        <v>-2483.9391085568859</v>
       </c>
       <c r="F14" s="36">
         <f>+'Balance sheet'!J13-'Balance sheet'!K13</f>
-        <v>-2782.9221848668531</v>
+        <v>-2582.7620423651315</v>
       </c>
       <c r="G14" s="159">
         <f>+'Balance sheet'!K13-'Balance sheet'!L13</f>
-        <v>-2896.613181047127</v>
+        <v>-2686.9787888637147</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -24556,23 +24557,23 @@
       </c>
       <c r="C15" s="459">
         <f>+'Balance sheet'!G14-'Balance sheet'!H14</f>
-        <v>738.79162331361522</v>
+        <v>977.21277331361625</v>
       </c>
       <c r="D15" s="459">
         <f>+'Balance sheet'!H14-'Balance sheet'!I14</f>
-        <v>-511.02530560399919</v>
+        <v>-468.43986347033388</v>
       </c>
       <c r="E15" s="459">
         <f>+'Balance sheet'!I14-'Balance sheet'!J14</f>
-        <v>-157.32839153290706</v>
+        <v>-144.21769223849788</v>
       </c>
       <c r="F15" s="459">
         <f>+'Balance sheet'!J14-'Balance sheet'!K14</f>
-        <v>-165.85667212571661</v>
+        <v>-152.03528278190743</v>
       </c>
       <c r="G15" s="460">
         <f>+'Balance sheet'!K14-'Balance sheet'!L14</f>
-        <v>-174.9092248927227</v>
+        <v>-160.33345615166309</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -24701,23 +24702,23 @@
       </c>
       <c r="C20" s="36">
         <f>+'Balance sheet'!G19-'Balance sheet'!H19</f>
-        <v>-98.572386444497624</v>
+        <v>8.2557145559794662</v>
       </c>
       <c r="D20" s="36">
         <f>+'Balance sheet'!H19-'Balance sheet'!I19</f>
-        <v>-228.97240014513545</v>
+        <v>-209.89136679970829</v>
       </c>
       <c r="E20" s="36">
         <f>+'Balance sheet'!I19-'Balance sheet'!J19</f>
-        <v>-70.493298522047326</v>
+        <v>-64.618856978543363</v>
       </c>
       <c r="F20" s="36">
         <f>+'Balance sheet'!J19-'Balance sheet'!K19</f>
-        <v>-74.314520005666736</v>
+        <v>-68.121643338527747</v>
       </c>
       <c r="G20" s="159">
         <f>+'Balance sheet'!K19-'Balance sheet'!L19</f>
-        <v>-78.370649343628884</v>
+        <v>-71.839761898326969</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -24750,23 +24751,23 @@
       </c>
       <c r="C23" s="36">
         <f>+'Balance sheet'!H22-'Balance sheet'!G22</f>
-        <v>147.94462640610516</v>
+        <v>177.88544426309056</v>
       </c>
       <c r="D23" s="36">
         <f>+'Balance sheet'!I22-'Balance sheet'!H22</f>
-        <v>135.36528693810908</v>
+        <v>143.62685552251958</v>
       </c>
       <c r="E23" s="36">
         <f>+'Balance sheet'!J22-'Balance sheet'!I22</f>
-        <v>25.774821995500815</v>
+        <v>40.301086069787061</v>
       </c>
       <c r="F23" s="36">
         <f>+'Balance sheet'!K22-'Balance sheet'!J22</f>
-        <v>53.355984417772106</v>
+        <v>42.072016215950043</v>
       </c>
       <c r="G23" s="159">
         <f>+'Balance sheet'!L22-'Balance sheet'!K22</f>
-        <v>51.955161783551603</v>
+        <v>30.699054170904674</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -24779,23 +24780,23 @@
       </c>
       <c r="C24" s="459">
         <f>+'Balance sheet'!H23-'Balance sheet'!G23</f>
-        <v>-50.0818225951881</v>
+        <v>-108.72684919990047</v>
       </c>
       <c r="D24" s="459">
         <f>+'Balance sheet'!I23-'Balance sheet'!H23</f>
-        <v>125.6981297289592</v>
+        <v>115.22328558487959</v>
       </c>
       <c r="E24" s="459">
         <f>+'Balance sheet'!J23-'Balance sheet'!I23</f>
-        <v>38.698444777755071</v>
+        <v>35.473574379608863</v>
       </c>
       <c r="F24" s="459">
         <f>+'Balance sheet'!K23-'Balance sheet'!J23</f>
-        <v>40.796166570715968</v>
+        <v>37.396486023156399</v>
       </c>
       <c r="G24" s="460">
         <f>+'Balance sheet'!L23-'Balance sheet'!K23</f>
-        <v>43.022844857695418</v>
+        <v>39.437607786220951</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -24808,23 +24809,23 @@
       </c>
       <c r="C25" s="36">
         <f ca="1">+'Balance sheet'!H24-'Balance sheet'!G24</f>
-        <v>-124.17426977703326</v>
+        <v>-11.695886573990265</v>
       </c>
       <c r="D25" s="36">
         <f ca="1">+'Balance sheet'!I24-'Balance sheet'!H24</f>
-        <v>180.19784924740748</v>
+        <v>206.69337023533876</v>
       </c>
       <c r="E25" s="36">
         <f ca="1">+'Balance sheet'!J24-'Balance sheet'!I24</f>
-        <v>2.8412298990372165</v>
+        <v>37.022267254083317</v>
       </c>
       <c r="F25" s="36">
         <f ca="1">+'Balance sheet'!K24-'Balance sheet'!J24</f>
-        <v>62.377368380955431</v>
+        <v>41.969190949156882</v>
       </c>
       <c r="G25" s="159">
         <f ca="1">+'Balance sheet'!L24-'Balance sheet'!K24</f>
-        <v>55.106036526679418</v>
+        <v>14.05893663792267</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -24895,23 +24896,23 @@
       </c>
       <c r="C28" s="459">
         <f>+'Balance sheet'!H27-'Balance sheet'!G27</f>
-        <v>5.1094431600736243</v>
+        <v>-181.43220586324833</v>
       </c>
       <c r="D28" s="459">
         <f>+'Balance sheet'!I27-'Balance sheet'!H27</f>
-        <v>399.82821658236571</v>
+        <v>366.5091985338363</v>
       </c>
       <c r="E28" s="459">
         <f>+'Balance sheet'!J27-'Balance sheet'!I27</f>
-        <v>123.09435465240858</v>
+        <v>112.83649176470772</v>
       </c>
       <c r="F28" s="459">
         <f>+'Balance sheet'!K27-'Balance sheet'!J27</f>
-        <v>129.76691505703911</v>
+        <v>118.9530054689526</v>
       </c>
       <c r="G28" s="460">
         <f>+'Balance sheet'!L27-'Balance sheet'!K27</f>
-        <v>136.84966808053514</v>
+        <v>125.44552907382467</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -24964,23 +24965,23 @@
       </c>
       <c r="C31" s="36">
         <f ca="1">+'Balance sheet'!H30-'Balance sheet'!G30</f>
-        <v>731.72845300325389</v>
+        <v>873.02400370481337</v>
       </c>
       <c r="D31" s="36">
         <f ca="1">+'Balance sheet'!I30-'Balance sheet'!H30</f>
-        <v>895.32793633856818</v>
+        <v>1069.5163285622575</v>
       </c>
       <c r="E31" s="36">
         <f ca="1">+'Balance sheet'!J30-'Balance sheet'!I30</f>
-        <v>819.05872791132424</v>
+        <v>1035.0844812011173</v>
       </c>
       <c r="F31" s="36">
         <f ca="1">+'Balance sheet'!K30-'Balance sheet'!J30</f>
-        <v>815.55545191185047</v>
+        <v>1007.1130858210199</v>
       </c>
       <c r="G31" s="159">
         <f ca="1">+'Balance sheet'!L30-'Balance sheet'!K30</f>
-        <v>797.98403286835855</v>
+        <v>939.96273787975042</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -25022,23 +25023,23 @@
       </c>
       <c r="C33" s="36">
         <f>+'Balance sheet'!H32-'Balance sheet'!G32</f>
-        <v>429.26024719294674</v>
+        <v>-35.951752807055527</v>
       </c>
       <c r="D33" s="36">
         <f>+'Balance sheet'!I32-'Balance sheet'!H32</f>
-        <v>997.12254751999899</v>
+        <v>914.02900189333468</v>
       </c>
       <c r="E33" s="36">
         <f>+'Balance sheet'!J32-'Balance sheet'!I32</f>
-        <v>306.98222738128061</v>
+        <v>281.40037509950798</v>
       </c>
       <c r="F33" s="36">
         <f>+'Balance sheet'!K32-'Balance sheet'!J32</f>
-        <v>323.62277487944903</v>
+        <v>296.65421030616108</v>
       </c>
       <c r="G33" s="159">
         <f>+'Balance sheet'!L32-'Balance sheet'!K32</f>
-        <v>341.28629247360368</v>
+        <v>312.8457681008058</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -25051,23 +25052,23 @@
       </c>
       <c r="C34" s="459">
         <f>+'Balance sheet'!H33-'Balance sheet'!G33</f>
-        <v>-1634.8903600000003</v>
+        <v>-1560.0306100000003</v>
       </c>
       <c r="D34" s="459">
         <f>+'Balance sheet'!I33-'Balance sheet'!H33</f>
-        <v>338.4480539999995</v>
+        <v>359.10410159999992</v>
       </c>
       <c r="E34" s="459">
         <f>+'Balance sheet'!J33-'Balance sheet'!I33</f>
-        <v>64.443688215000748</v>
+        <v>100.76308677750012</v>
       </c>
       <c r="F34" s="459">
         <f>+'Balance sheet'!K33-'Balance sheet'!J33</f>
-        <v>133.40369236395009</v>
+        <v>105.19086789698986</v>
       </c>
       <c r="G34" s="460">
         <f>+'Balance sheet'!L33-'Balance sheet'!K33</f>
-        <v>129.90127527257255</v>
+        <v>76.755535919143767</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -25080,23 +25081,23 @@
       </c>
       <c r="C35" s="36">
         <f>+'Balance sheet'!H34-'Balance sheet'!G34</f>
-        <v>-35.358435997048218</v>
+        <v>-76.762608455163672</v>
       </c>
       <c r="D35" s="36">
         <f>+'Balance sheet'!I34-'Balance sheet'!H34</f>
-        <v>88.74455929639214</v>
+        <v>81.349179355026422</v>
       </c>
       <c r="E35" s="36">
         <f>+'Balance sheet'!J34-'Balance sheet'!I34</f>
-        <v>27.32161914153312</v>
+        <v>25.044817546405397</v>
       </c>
       <c r="F35" s="36">
         <f>+'Balance sheet'!K34-'Balance sheet'!J34</f>
-        <v>28.802638759280626</v>
+        <v>26.402418862673926</v>
       </c>
       <c r="G35" s="159">
         <f>+'Balance sheet'!L34-'Balance sheet'!K34</f>
-        <v>30.374703385054318</v>
+        <v>27.843478102966515</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -25138,23 +25139,23 @@
       </c>
       <c r="C37" s="36">
         <f>+'Balance sheet'!H36-'Balance sheet'!G36</f>
-        <v>58.380109929860168</v>
+        <v>70.194991486170579</v>
       </c>
       <c r="D37" s="36">
         <f>+'Balance sheet'!I36-'Balance sheet'!H36</f>
-        <v>53.416203914302855</v>
+        <v>56.676283674327578</v>
       </c>
       <c r="E37" s="36">
         <f>+'Balance sheet'!J36-'Balance sheet'!I36</f>
-        <v>10.170946914891204</v>
+        <v>15.903124650087534</v>
       </c>
       <c r="F37" s="36">
         <f>+'Balance sheet'!K36-'Balance sheet'!J36</f>
-        <v>21.054689929562073</v>
+        <v>16.601947575411714</v>
       </c>
       <c r="G37" s="159">
         <f>+'Balance sheet'!L36-'Balance sheet'!K36</f>
-        <v>20.501914331254397</v>
+        <v>12.114087552734361</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -25216,23 +25217,23 @@
       </c>
       <c r="C41" s="459">
         <f>+'Balance sheet'!H40-'Balance sheet'!G40</f>
-        <v>-26.778996000000006</v>
+        <v>-27.610771</v>
       </c>
       <c r="D41" s="459">
         <f>+'Balance sheet'!I40-'Balance sheet'!H40</f>
-        <v>-61.079059866666626</v>
+        <v>-63.201633146666666</v>
       </c>
       <c r="E41" s="459">
         <f>+'Balance sheet'!J40-'Balance sheet'!I40</f>
-        <v>-62.511141827000017</v>
+        <v>-65.440812852833346</v>
       </c>
       <c r="F41" s="459">
         <f>+'Balance sheet'!K40-'Balance sheet'!J40</f>
-        <v>-65.475668323976663</v>
+        <v>-67.77838769498868</v>
       </c>
       <c r="G41" s="460">
         <f>+'Balance sheet'!L40-'Balance sheet'!K40</f>
-        <v>-102.54354499505075</v>
+        <v>-104.22609940645441</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -25245,23 +25246,23 @@
       </c>
       <c r="C42" s="36">
         <f>+'Balance sheet'!H41-'Balance sheet'!G41</f>
-        <v>-1205.0548200000012</v>
+        <v>-1242.4846949999992</v>
       </c>
       <c r="D42" s="36">
         <f>+'Balance sheet'!I41-'Balance sheet'!H41</f>
-        <v>-1374.2788469999978</v>
+        <v>-1422.0367458000001</v>
       </c>
       <c r="E42" s="36">
         <f>+'Balance sheet'!J41-'Balance sheet'!I41</f>
-        <v>-1406.5006911074997</v>
+        <v>-1472.4182891887504</v>
       </c>
       <c r="F42" s="36">
         <f>+'Balance sheet'!K41-'Balance sheet'!J41</f>
-        <v>-1473.202537289475</v>
+        <v>-1525.0137231372464</v>
       </c>
       <c r="G42" s="159">
         <f>+'Balance sheet'!L41-'Balance sheet'!K41</f>
-        <v>-1538.1531749257629</v>
+        <v>-1563.391491096816</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -25414,23 +25415,23 @@
       </c>
       <c r="C51" s="468">
         <f t="shared" ref="C51:E51" ca="1" si="0">+SUM(C6:C47)+C2</f>
-        <v>4200.1447478653608</v>
+        <v>5326.1378346143938</v>
       </c>
       <c r="D51" s="468">
         <f t="shared" ca="1" si="0"/>
-        <v>7901.0438955053141</v>
+        <v>9408.7529746477703</v>
       </c>
       <c r="E51" s="468">
         <f t="shared" ca="1" si="0"/>
-        <v>7256.3157527199637</v>
+        <v>9139.8971339335094</v>
       </c>
       <c r="F51" s="468">
         <f ca="1">+SUM(F6:F47)+F2</f>
-        <v>7723.8663149187641</v>
+        <v>9344.6590272460817</v>
       </c>
       <c r="G51" s="468">
         <f ca="1">+SUM(G6:G47)+G2</f>
-        <v>8182.1351978390358</v>
+        <v>9399.7043724129999</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -25519,23 +25520,23 @@
       </c>
       <c r="C56" s="468">
         <f t="shared" ref="C56:G56" ca="1" si="1">+C51-C53-C54</f>
-        <v>1085.2556152478996</v>
+        <v>2211.2487019969321</v>
       </c>
       <c r="D56" s="468">
         <f t="shared" ca="1" si="1"/>
-        <v>4283.945249747112</v>
+        <v>5791.6543288895682</v>
       </c>
       <c r="E56" s="468">
         <f t="shared" ca="1" si="1"/>
-        <v>3139.6487574402081</v>
+        <v>5023.2301386537538</v>
       </c>
       <c r="F56" s="468">
         <f t="shared" ca="1" si="1"/>
-        <v>3109.9012487113287</v>
+        <v>4730.6939610386453</v>
       </c>
       <c r="G56" s="468">
         <f t="shared" ca="1" si="1"/>
-        <v>3072.8051322974206</v>
+        <v>4290.3743068713848</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -25561,19 +25562,19 @@
       </c>
       <c r="D58" s="209">
         <f t="shared" ref="D58:G58" ca="1" si="2">+C59</f>
-        <v>8732.2556152478992</v>
+        <v>9858.2487019969321</v>
       </c>
       <c r="E58" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>13016.200864995011</v>
+        <v>15649.9030308865</v>
       </c>
       <c r="F58" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>16155.84962243522</v>
+        <v>20673.133169540255</v>
       </c>
       <c r="G58" s="209">
         <f t="shared" ca="1" si="2"/>
-        <v>19265.750871146549</v>
+        <v>25403.827130578902</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -25586,23 +25587,23 @@
       </c>
       <c r="C59" s="246">
         <f t="shared" ref="C59:G59" ca="1" si="3">+C58+C56</f>
-        <v>8732.2556152478992</v>
+        <v>9858.2487019969321</v>
       </c>
       <c r="D59" s="246">
         <f t="shared" ca="1" si="3"/>
-        <v>13016.200864995011</v>
+        <v>15649.9030308865</v>
       </c>
       <c r="E59" s="246">
         <f t="shared" ca="1" si="3"/>
-        <v>16155.84962243522</v>
+        <v>20673.133169540255</v>
       </c>
       <c r="F59" s="246">
         <f t="shared" ca="1" si="3"/>
-        <v>19265.750871146549</v>
+        <v>25403.827130578902</v>
       </c>
       <c r="G59" s="246">
         <f t="shared" ca="1" si="3"/>
-        <v>22338.55600344397</v>
+        <v>29694.201437450287</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -25624,23 +25625,23 @@
       </c>
       <c r="C61" s="468">
         <f t="shared" ca="1" si="4"/>
-        <v>4200.1447478653608</v>
+        <v>5326.1378346143938</v>
       </c>
       <c r="D61" s="468">
         <f t="shared" ca="1" si="4"/>
-        <v>7901.0438955053141</v>
+        <v>9408.7529746477703</v>
       </c>
       <c r="E61" s="468">
         <f t="shared" ca="1" si="4"/>
-        <v>7256.3157527199637</v>
+        <v>9139.8971339335094</v>
       </c>
       <c r="F61" s="468">
         <f t="shared" ca="1" si="4"/>
-        <v>7723.8663149187641</v>
+        <v>9344.6590272460817</v>
       </c>
       <c r="G61" s="468">
         <f t="shared" ca="1" si="4"/>
-        <v>8182.1351978390358</v>
+        <v>9399.7043724129999</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -26194,19 +26195,19 @@
       </c>
       <c r="I17" s="272">
         <f t="shared" ref="I17:L17" ca="1" si="4">+H21</f>
-        <v>9767.0235026883638</v>
+        <v>10747.255490698757</v>
       </c>
       <c r="J17" s="272">
         <f t="shared" ca="1" si="4"/>
-        <v>17171.234318478815</v>
+        <v>19362.602726727138</v>
       </c>
       <c r="K17" s="272">
         <f t="shared" ca="1" si="4"/>
-        <v>24100.637670822147</v>
+        <v>27801.025036776173</v>
       </c>
       <c r="L17" s="273">
         <f t="shared" ca="1" si="4"/>
-        <v>31076.352222514601</v>
+        <v>36107.904386415212</v>
       </c>
       <c r="M17" s="266"/>
     </row>
@@ -26240,23 +26241,23 @@
       </c>
       <c r="H18" s="487">
         <f ca="1">'Income statement'!H24</f>
-        <v>9450.9126353058255</v>
+        <v>10431.144623316219</v>
       </c>
       <c r="I18" s="487">
         <f ca="1">'Income statement'!I24</f>
-        <v>11021.30946154865</v>
+        <v>12232.445881786582</v>
       </c>
       <c r="J18" s="487">
         <f ca="1">'Income statement'!J24</f>
-        <v>11046.07034762309</v>
+        <v>12555.089305328791</v>
       </c>
       <c r="K18" s="487">
         <f ca="1">'Income statement'!K24</f>
-        <v>11589.67961789989</v>
+        <v>12920.844415846477</v>
       </c>
       <c r="L18" s="488">
         <f ca="1">'Income statement'!L24</f>
-        <v>12069.920337918158</v>
+        <v>13043.365908576558</v>
       </c>
       <c r="M18" s="266"/>
     </row>
@@ -26355,23 +26356,23 @@
       </c>
       <c r="H21" s="557">
         <f t="shared" ref="H21:L21" ca="1" si="7">+H17+H18-H19-H20</f>
-        <v>9767.0235026883638</v>
+        <v>10747.255490698757</v>
       </c>
       <c r="I21" s="557">
         <f t="shared" ca="1" si="7"/>
-        <v>17171.234318478815</v>
+        <v>19362.602726727138</v>
       </c>
       <c r="J21" s="557">
         <f t="shared" ca="1" si="7"/>
-        <v>24100.637670822147</v>
+        <v>27801.025036776173</v>
       </c>
       <c r="K21" s="557">
         <f t="shared" ca="1" si="7"/>
-        <v>31076.352222514601</v>
+        <v>36107.904386415212</v>
       </c>
       <c r="L21" s="495">
         <f t="shared" ca="1" si="7"/>
-        <v>38036.94249489114</v>
+        <v>44041.940229450156</v>
       </c>
       <c r="M21" s="266"/>
     </row>
@@ -26499,23 +26500,23 @@
       </c>
       <c r="H27" s="209">
         <f>+H29*'Income statement'!H3</f>
-        <v>26.778995999999999</v>
+        <v>27.610771</v>
       </c>
       <c r="I27" s="209">
         <f>+I29*'Income statement'!I3</f>
-        <v>61.079059866666654</v>
+        <v>63.201633146666659</v>
       </c>
       <c r="J27" s="209">
         <f>+J29*'Income statement'!J3</f>
-        <v>62.511141827000003</v>
+        <v>65.440812852833332</v>
       </c>
       <c r="K27" s="209">
         <f>+K29*'Income statement'!K3</f>
-        <v>65.475668323976663</v>
+        <v>67.778387694988666</v>
       </c>
       <c r="L27" s="210">
         <f>+L29*'Income statement'!L3</f>
-        <v>102.54354499505077</v>
+        <v>104.22609940645445</v>
       </c>
       <c r="M27" s="266"/>
     </row>
@@ -26548,23 +26549,23 @@
       </c>
       <c r="H28" s="558">
         <f t="shared" ref="H28:L28" si="8">+G28+H27</f>
-        <v>327.77899600000001</v>
+        <v>328.610771</v>
       </c>
       <c r="I28" s="558">
         <f t="shared" si="8"/>
-        <v>388.85805586666663</v>
+        <v>391.81240414666667</v>
       </c>
       <c r="J28" s="558">
         <f t="shared" si="8"/>
-        <v>451.36919769366665</v>
+        <v>457.25321699950001</v>
       </c>
       <c r="K28" s="558">
         <f t="shared" si="8"/>
-        <v>516.84486601764331</v>
+        <v>525.03160469448869</v>
       </c>
       <c r="L28" s="489">
         <f t="shared" si="8"/>
-        <v>619.38841101269406</v>
+        <v>629.2577041009431</v>
       </c>
       <c r="M28" s="266"/>
     </row>
@@ -26774,23 +26775,23 @@
       </c>
       <c r="H35" s="490">
         <f>+H39*'Income statement'!H3</f>
-        <v>1205.0548199999998</v>
+        <v>1242.4846949999999</v>
       </c>
       <c r="I35" s="490">
         <f>+I39*'Income statement'!I3</f>
-        <v>1374.2788469999996</v>
+        <v>1422.0367457999998</v>
       </c>
       <c r="J35" s="490">
         <f>+J39*'Income statement'!J3</f>
-        <v>1406.5006911075</v>
+        <v>1472.4182891887499</v>
       </c>
       <c r="K35" s="490">
         <f>+K39*'Income statement'!K3</f>
-        <v>1473.202537289475</v>
+        <v>1525.0137231372448</v>
       </c>
       <c r="L35" s="491">
         <f>+L39*'Income statement'!L3</f>
-        <v>1538.1531749257613</v>
+        <v>1563.3914910968167</v>
       </c>
       <c r="M35" s="266"/>
     </row>
@@ -26844,23 +26845,23 @@
       </c>
       <c r="H37" s="560">
         <f>+G37-H35</f>
-        <v>27641.945179999999</v>
+        <v>27604.515305000001</v>
       </c>
       <c r="I37" s="560">
         <f t="shared" ref="I37:L37" si="10">+H37-I35</f>
-        <v>26267.666333000001</v>
+        <v>26182.478559200001</v>
       </c>
       <c r="J37" s="560">
         <f t="shared" si="10"/>
-        <v>24861.165641892501</v>
+        <v>24710.06027001125</v>
       </c>
       <c r="K37" s="560">
         <f t="shared" si="10"/>
-        <v>23387.963104603026</v>
+        <v>23185.046546874004</v>
       </c>
       <c r="L37" s="496">
         <f t="shared" si="10"/>
-        <v>21849.809929677263</v>
+        <v>21621.655055777188</v>
       </c>
       <c r="M37" s="266"/>
       <c r="N37" s="4"/>
@@ -27247,6 +27248,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="0c3a1246-0cb1-4231-aa54-e583c82ab35b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008AE9AC42CCF6CD49BED1E9721BF95A04" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="24922925328db1cd0dbe5fb272446f0e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="0c3a1246-0cb1-4231-aa54-e583c82ab35b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="29819d30454c4a022fc0140fd60984c3" ns3:_="">
     <xsd:import namespace="0c3a1246-0cb1-4231-aa54-e583c82ab35b"/>
@@ -27428,24 +27446,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A4BB476-DE76-4027-A229-93338CEA3DFC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="0c3a1246-0cb1-4231-aa54-e583c82ab35b"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="0c3a1246-0cb1-4231-aa54-e583c82ab35b" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CDBCF37-2048-4611-8F92-E16168C97416}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79F2B660-F8F2-4D05-B13D-B94C17B52C77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -27461,28 +27486,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CDBCF37-2048-4611-8F92-E16168C97416}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4A4BB476-DE76-4027-A229-93338CEA3DFC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="0c3a1246-0cb1-4231-aa54-e583c82ab35b"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>